--- a/2025-armada-prime-tech-1099-k1.xlsx
+++ b/2025-armada-prime-tech-1099-k1.xlsx
@@ -554,7 +554,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>AUG ANOMALY: Aug used a different waterfall (9.5% Consultant + 13.5% Trader &amp; Developer + 5.5% Mgmt + 1.5% to principals = 30%). TruQuant moved upstream from Sep onwards. See 1099 Summary + Distributions Ledger tabs.</t>
+          <t>TruQuant payments excluded entirely (per Nairne 2026-04-30) — TQ is not a GP expense / 1099 recipient. Aug TQ-tagged ~$6,999 stays in retained earnings → flows to K-1 net income.</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>60625.41</v>
+        <v>53544.62</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>146622.24</v>
+        <v>139541.45</v>
       </c>
       <c r="C14" s="7">
         <f> sum of all non-member contractor payments</f>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>-86718.15000000002</v>
+        <v>-79637.36000000002</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>-42412.10500000001</v>
+        <v>-38871.71000000001</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>-42412.10500000001</v>
+        <v>-38871.71000000001</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -992,11 +992,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trader &amp; Developer (TruQuant)</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>6909.93</v>
+        <v>4152.7</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1014,11 +1014,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Issac</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>4152.7</v>
+        <v>761.49</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1036,11 +1036,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>761.49</v>
+        <v>164.9</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1056,75 +1056,31 @@
       <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Spydr (TruQuant)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>170.86</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Individual 1099</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>From Distributions ledger (cash actually paid)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Luke</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>164.9</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Individual 1099</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>From Distributions ledger (cash actually paid)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-    </row>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL 1099 PAYMENTS</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>139541.45</v>
+      </c>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+    </row>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL 1099 PAYMENTS</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>146622.24</v>
-      </c>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Cross-check: 1099 total ($146,622.24) + Raj K-1 direct ($946.97) + Nairne K-1 direct ($946.97) = $148,516.18</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Should approx equal Gross Perf Fees Crystallized (TPA): $153,023.03 — delta = $4,506.85 (= cash-vs-accrual timing + Aug TQ-T&amp;D treatment)</t>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Cross-check: 1099 total ($139,541.45) + Raj K-1 direct ($946.97) + Nairne K-1 direct ($946.97) = $141,435.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Should approx equal Gross Perf Fees Crystallized (TPA): $153,023.03 — delta = $11,587.64 (= cash-vs-accrual timing + Aug TQ-T&amp;D treatment)</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1205,10 +1161,10 @@
         <v>946.97</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>-43359.07500000001</v>
+        <v>-39818.68000000001</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>-42412.10500000001</v>
+        <v>-38871.71000000001</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -1222,10 +1178,10 @@
         <v>946.97</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>-43359.07500000001</v>
+        <v>-39818.68000000001</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>-42412.10500000001</v>
+        <v>-38871.71000000001</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
@@ -1247,7 +1203,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Less: 1099 contractor payments (incl. Fund Mgmt + Phil + consultants + Aug Trader &amp; Developer): $144,728.30</t>
+          <t>Less: 1099 contractor payments (incl. Fund Mgmt + Phil + consultants + Aug Trader &amp; Developer): $137,647.51</t>
         </is>
       </c>
     </row>
@@ -1267,14 +1223,14 @@
     </row>
     <row r="13">
       <c r="A13">
-        <f> GP Net Income (residual): $-86,718.15</f>
+        <f> GP Net Income (residual): $-79,637.36</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Per K-1 member (50/50): $-43,359.08</t>
+          <t>Per K-1 member (50/50): $-39,818.68</t>
         </is>
       </c>
     </row>
@@ -1307,10 +1263,18 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>TruQuant payments are excluded per Nairne 2026-04-30 (TQ is not a GP expense). Aug TQ-tagged ~$6,999 effectively flows into GP retained earnings → increases the K-1 net income line above.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A19:E19"/>
@@ -2420,11 +2384,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -2563,57 +2527,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Trader &amp; Developer (TruQuant)</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>6909.93</v>
+        <v>335.47</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>285.77</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>1268.23</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>1833.52</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0</v>
+        <v>429.71</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>6909.93</v>
+        <v>4152.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Raj</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>335.47</v>
+        <v>255.92</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>285.77</v>
+        <v>62.32</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1268.23</v>
+        <v>262.24</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1833.52</v>
+        <v>287.26</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>429.71</v>
+        <v>79.23</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>4152.7</v>
+        <v>946.97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Raj</t>
+          <t>Nairne</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
@@ -2638,7 +2602,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nairne</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
@@ -2663,32 +2627,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Issac</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>255.92</v>
+        <v>0</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>62.32</v>
+        <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>262.24</v>
+        <v>254.12</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>287.26</v>
+        <v>785.85</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>79.23</v>
+        <v>-278.48</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>946.97</v>
+        <v>761.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
@@ -2698,141 +2662,91 @@
         <v>0</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>254.12</v>
+        <v>0</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>785.85</v>
+        <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-278.48</v>
+        <v>164.9</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>761.49</v>
+        <v>164.9</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Spydr (TruQuant)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>82.08</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="17" t="n">
-        <v>170.86</v>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>MONTH TOTAL (cash actually paid out)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>8356.690000000001</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>12381.17</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>48583.18</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>56973.74000000001</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>15140.61</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>141435.39</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Luke</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>164.9</v>
-      </c>
-      <c r="G15" s="17" t="n">
-        <v>164.9</v>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>TPA Perf Fees Crystallized (what was OWED)</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>15355.51</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>12474.75</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>51906.99</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>57074.08999999997</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>16211.69</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>153023.03</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>MONTH TOTAL (cash actually paid out)</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>15355.4</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>12463.25</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>48583.18</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>56973.74000000001</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>15140.61</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>148516.18</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>TPA Perf Fees Crystallized (what was OWED)</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="n">
-        <v>15355.51</v>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>12474.75</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>51906.99</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>57074.08999999997</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>16211.69</v>
-      </c>
-      <c r="G17" s="22" t="n">
-        <v>153023.03</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>DELTA (Owed - Paid; positive = unpaid liability)</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>0.1100000000024011</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>11.50000000000182</v>
-      </c>
-      <c r="D18" s="13" t="n">
+      <c r="B16" s="13" t="n">
+        <v>6998.820000000002</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>93.58000000000175</v>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>3323.809999999998</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E16" s="13" t="n">
         <v>100.3499999999622</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F16" s="13" t="n">
         <v>1071.080000000004</v>
       </c>
-      <c r="G18" s="13" t="n">
-        <v>4506.849999999977</v>
+      <c r="G16" s="13" t="n">
+        <v>11587.63999999996</v>
       </c>
     </row>
   </sheetData>

--- a/2025-armada-prime-tech-1099-k1.xlsx
+++ b/2025-armada-prime-tech-1099-k1.xlsx
@@ -74,7 +74,7 @@
       <color rgb="00999999"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +97,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00EEEEEE"/>
         <bgColor rgb="00EEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FD"/>
+        <bgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,7 +148,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -155,7 +160,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -521,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -620,7 +629,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>LESS: 1099 PAYMENTS TO CONTRACTORS (ACTUAL PAID per Distributions Ledger)</t>
+          <t>LESS: 1099 EXPENSES (contractor payments — partners excluded)</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -629,208 +638,215 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Fund Mgmt entity</t>
+          <t xml:space="preserve">  Consultant pool (Alec, Jake, AJ, Issac, Luke)</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>85049.86</v>
+        <v>53544.62</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Recipient entity name TBD — likely Armada Capital Group LLC</t>
+          <t>See 1099 Summary tab for per-consultant breakdown</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Consultants (incl. Aug Trader &amp; Developer to TruQuant)</t>
+          <t xml:space="preserve">  Phil (0.5% GP fixed slice)</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>53544.62</v>
+        <v>946.97</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>See 1099 Summary tab for per-consultant breakdown</t>
+          <t>Phil held the 0.5% slice in 2025 as a 1099 contractor</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Phil — fixed 0.5% slice</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>946.97</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Phil held the 0.5% GP slice in 2025 (Alec took it over in 2026-04)</t>
-        </is>
-      </c>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOTAL 1099 EXPENSES</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>54491.59</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOTAL 1099 PAYMENTS</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>139541.45</v>
-      </c>
-      <c r="C14" s="7">
-        <f> sum of all non-member contractor payments</f>
-        <v/>
-      </c>
+      <c r="A14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>LESS: GP-PAID OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>LESS: GP-PAID OPERATING EXPENSES</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Vendor expenses (Chris, Insurance, PVD, Website, etc.)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>91225</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>See GP Expenses tab. Includes items likely needing reclass (SPV loans → balance sheet, Insurance pro-rata).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Vendor expenses (Chris, Insurance, PVD, Website, etc.)</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>91225</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>See GP Expenses tab. Sum of Aug-Dec Distributions Ledger Costs sections + Dec BEST ONE Costs.</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PARTNERSHIP NET INCOME (allocated to K-1 partners)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>7306.439999999973</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Gross - 1099 expenses - Op expenses. This is what flows to K-1s.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>LESS: K-1 MEMBER DISTRIBUTIONS</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="A19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Raj Duggal (0.5% direct)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>946.97</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>K-1 ALLOCATION (per ownership: Nairne 60% / Raj 0.5%)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Nairne (0.5% direct)</t>
+          <t xml:space="preserve">  Nairne — Fund Mgmt 59.5% slice received as cash</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
+        <v>85049.86</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Reported as K-1 income (partner allocation, not expense)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Nairne — direct 0.5% slice received as cash</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
         <v>946.97</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Reported as K-1 income</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>NET INCOME (residual to GP)</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>-79637.36000000002</v>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Gross - 1099s - Op Expenses - Direct Member Slices</t>
-        </is>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Nairne — TOTAL cash received (60% of perf fees)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>85996.83</v>
+      </c>
+      <c r="C23">
+        <f> Fund Mgmt + direct slice</f>
+        <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Raj — direct 0.5% slice received as cash</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>946.97</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Reported as K-1 income</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>K-1 ALLOCATION (50/50 of net income, per Nairne 2026-04-30)</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="inlineStr"/>
+      <c r="A25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Raj Duggal — total K-1 income</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>-38871.71000000001</v>
+          <t>(K-1 net income vs cash distributions reconcile on accountant's K-1 forms)</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Direct slice + 50% of residual net income</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Nairne — total K-1 income</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>-38871.71000000001</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Direct slice + 50% of residual net income</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
+          <t>Cash received above is what each partner got operationally. The K-1 'net income' line above is the partnership's taxable income — accountant allocates it per the operating agreement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>CROSS-CHECK</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>CHECK: 1099s + Phil + Raj + Nairne = Gross</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Total cash out (1099s $54,491.59 + Nairne K-1 $85,996.83 + Raj K-1 $946.97)</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>153023.0299999999</v>
+        <v>141435.39</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Should equal 153,023.03</t>
+          <t>vs Gross $153,023.03 — delta $11,587.64 (= retained / cash-vs-accrual / TQ exclusion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Operating expenses + retained should equal the delta above (with cash-vs-accrual smoothing).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -843,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -904,20 +920,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fund Mgmt entity (TBD — Armada Capital Group LLC?)</t>
+          <t>Phil (last name TBD)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>85049.86</v>
+        <v>946.97</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Entity 1099</t>
+          <t>Individual 1099</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>59.5% slice (Sep-Dec) + 5.5% slice (Aug)</t>
+          <t>0.5% GP fixed slice (held by Phil all 2025)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -926,11 +942,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Phil (last name TBD)</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>946.97</v>
+        <v>38076.87</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -939,7 +955,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.5% GP fixed slice (held by Phil all 2025)</t>
+          <t>From Distributions ledger (cash actually paid)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -948,11 +964,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>38076.87</v>
+        <v>10388.66</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -970,11 +986,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>10388.66</v>
+        <v>4152.7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -992,11 +1008,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Issac</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4152.7</v>
+        <v>761.49</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1014,11 +1030,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>761.49</v>
+        <v>164.9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1034,53 +1050,31 @@
       <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Luke</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>164.9</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Individual 1099</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>From Distributions ledger (cash actually paid)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>TOTAL 1099 PAYMENTS</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>139541.45</v>
-      </c>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="B11" s="12" t="n">
+        <v>54491.59</v>
+      </c>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>K-1 partner cash distributions (NOT on 1099s): Nairne $85,996.83 + Raj $946.97 = $86,943.80</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Cross-check: 1099 total ($139,541.45) + Raj K-1 direct ($946.97) + Nairne K-1 direct ($946.97) = $141,435.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Should approx equal Gross Perf Fees Crystallized (TPA): $153,023.03 — delta = $11,587.64 (= cash-vs-accrual timing + Aug TQ-T&amp;D treatment)</t>
+          <t>Cross-check: 1099 total ($54,491.59) + K-1 cash ($86,943.80) = $141,435.39; Gross perf fees per TPA = $153,023.03; delta = $11,587.64 (cash-vs-accrual timing + Aug TQ-T&amp;D excluded)</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1119,7 +1113,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Members per Nairne 2026-04-30: Raj Duggal (50%) and Nairne (50%) of GP net income.</t>
+          <t>Members per Nairne 2026-04-30: Nairne (60% — Fund Mgmt 59.5% + direct 0.5%) and Raj Duggal (0.5%). Net income allocated per the operating agreement.</t>
         </is>
       </c>
     </row>
@@ -1132,17 +1126,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Direct 0.5% Slice ($)</t>
+          <t>Ownership %</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Share of GP Net Income (50%)</t>
+          <t>Cash Distributions ($)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Total K-1 Income ($)</t>
+          <t>Allocated Share of Net Income ($)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1154,34 +1148,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Raj Duggal</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>946.97</v>
+          <t>Nairne</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>99.17%</t>
+        </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>-39818.68000000001</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>-38871.71000000001</v>
+        <v>85996.83</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>7246.056198347081</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nairne</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+          <t>Raj Duggal</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
         <v>946.97</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>-39818.68000000001</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>-38871.71000000001</v>
+      <c r="D6" s="6" t="n">
+        <v>60.38380165289234</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
@@ -1203,75 +1201,90 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Less: 1099 contractor payments (incl. Fund Mgmt + Phil + consultants + Aug Trader &amp; Developer): $137,647.51</t>
+          <t>Less: 1099 contractor expenses (Alec/Jake/AJ/Phil/Issac/Luke): $54,491.59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Less: Direct 0.5% slices to Raj + Nairne: $1,893.94</t>
+          <t>Less: GP-paid operating expenses: $91,225.00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Less: GP-paid operating expenses: $91,225.00</t>
-        </is>
+      <c r="A12">
+        <f> Partnership NET INCOME (allocated to K-1s): $7,306.44</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <f> GP Net Income (residual): $-79,637.36</f>
-        <v/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Nairne allocated share (99.17%): $7,246.06</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Per K-1 member (50/50): $-39,818.68</t>
+          <t>Raj allocated share (0.83%): $60.38</t>
         </is>
       </c>
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>If Net Income is negative, the K-1s issue a loss — verify with accountant whether the loss can offset other income for the members.</t>
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Fund Mgmt 59.5% slice is Nairne's K-1 income (per Nairne 2026-04-30 — it's not a separate entity 1099).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Operating expenses include items that may be reclassed by the accountant (506c SPV Loans = capital not expense; Insurance $18k may be annual not Dec).</t>
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Cash distributions and allocated K-1 net income are different things in partnership tax — Schedule K-1 reports both. The accountant will compute capital account changes.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Operating expenses include items that may be reclassed by the accountant (506c SPV Loans → balance sheet; Insurance $18k may need annual proration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Cash-basis 1099s (above) may differ from accrual-basis (TPA-derived). Confirm GP's tax basis with accountant.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>TruQuant payments are excluded per Nairne 2026-04-30 (TQ is not a GP expense). Aug TQ-tagged ~$6,999 effectively flows into GP retained earnings → increases the K-1 net income line above.</t>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>TruQuant payments are excluded per Nairne 2026-04-30 (TQ is not a GP expense).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Ownership % shown (Nairne 99.17%/Raj 0.83%) is derived from the 60/0.5 split. The actual LLC operating agreement governs — confirm with the accountant before filing.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A20:E20"/>
@@ -1282,6 +1295,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A22:E22"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
@@ -1370,7 +1384,7 @@
           <t>Aug 2025</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="15" t="n">
         <v>18</v>
       </c>
       <c r="C4" s="6" t="n">
@@ -1401,7 +1415,7 @@
           <t>Sep 2025</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="15" t="n">
         <v>29</v>
       </c>
       <c r="C5" s="6" t="n">
@@ -1432,7 +1446,7 @@
           <t>Oct 2025</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>35</v>
       </c>
       <c r="C6" s="6" t="n">
@@ -1463,7 +1477,7 @@
           <t>Nov 2025</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>40</v>
       </c>
       <c r="C7" s="6" t="n">
@@ -1494,7 +1508,7 @@
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>45</v>
       </c>
       <c r="C8" s="6" t="n">
@@ -1647,7 +1661,7 @@
       <c r="F5" s="6" t="n">
         <v>4318.2789</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="16" t="n">
         <v>38691.4788</v>
       </c>
     </row>
@@ -1672,7 +1686,7 @@
       <c r="F6" s="6" t="n">
         <v>882.3828</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="16" t="n">
         <v>11298.2844</v>
       </c>
     </row>
@@ -1697,7 +1711,7 @@
       <c r="F7" s="6" t="n">
         <v>635.4503999999999</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="16" t="n">
         <v>4802.7564</v>
       </c>
     </row>
@@ -1722,7 +1736,7 @@
       <c r="F8" s="6" t="n">
         <v>374.5989</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>3173.6757</v>
       </c>
     </row>
@@ -1747,7 +1761,7 @@
       <c r="F9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="16" t="n">
         <v>1409.0037</v>
       </c>
     </row>
@@ -1772,7 +1786,7 @@
       <c r="F10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="16" t="n">
         <v>191.9346</v>
       </c>
     </row>
@@ -1797,7 +1811,7 @@
       <c r="F11" s="6" t="n">
         <v>74.38860000000001</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="16" t="n">
         <v>74.38860000000001</v>
       </c>
     </row>
@@ -1822,7 +1836,7 @@
       <c r="F12" s="6" t="n">
         <v>37.4595</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="16" t="n">
         <v>37.4595</v>
       </c>
     </row>
@@ -1969,17 +1983,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Aug 2025 subtotal</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="19" t="n">
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="18" t="n">
         <v>10275</v>
       </c>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1987,7 +2001,7 @@
           <t>Sep 2025</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>(no GP-paid op expenses recorded)</t>
         </is>
@@ -2094,17 +2108,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Oct 2025 subtotal</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n"/>
-      <c r="C13" s="19" t="n">
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="18" t="n">
         <v>43500</v>
       </c>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2182,17 +2196,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Nov 2025 subtotal</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="19" t="n">
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="18" t="n">
         <v>10350</v>
       </c>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2295,17 +2309,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Dec 2025 subtotal</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="19" t="n">
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="18" t="n">
         <v>27100</v>
       </c>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
     </row>
     <row r="23"/>
     <row r="24">
@@ -2323,42 +2337,42 @@
     </row>
     <row r="25"/>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Verify with user before sending to accountant</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>1. Insurance ($18k Dec): is this annual or already monthly-allocated? If annual, reduce to ~$1.5k for Dec.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>2. TPA fee duplication: Dec has TWO TPA lines ($600 + $4,500). The $600 also appears as fund-level admin in TPA's books. Confirm only the GP-paid portion goes here.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>3. 506c SPV Loan ($4,275 Aug + $25,000 Oct): is this an expense or a loan repayment? Expense for 1099/K-1 vs balance-sheet item.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>4. PVD ($6k Aug + $6k Oct): vendor identification needed for 1099 (if individual) or just expense (if entity).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>5. Badtwin / Ad Spend / Website (Oct): vendor names + 1099 obligations need confirmation.</t>
         </is>
@@ -2450,27 +2464,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Fund Mgmt</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Fund Mgmt 59.5% (= Nairne K-1)</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="n">
         <v>2815.16</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="22" t="n">
         <v>7415.62</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="22" t="n">
         <v>31206.94</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="22" t="n">
         <v>34183.9</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="22" t="n">
         <v>9428.24</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="23" t="n">
         <v>85049.86</v>
       </c>
     </row>
@@ -2495,7 +2509,7 @@
       <c r="F6" s="6" t="n">
         <v>4369.77</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="16" t="n">
         <v>38076.87</v>
       </c>
     </row>
@@ -2520,7 +2534,7 @@
       <c r="F7" s="6" t="n">
         <v>788.78</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="16" t="n">
         <v>10388.66</v>
       </c>
     </row>
@@ -2545,57 +2559,57 @@
       <c r="F8" s="6" t="n">
         <v>429.71</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>4152.7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Raj</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Raj (K-1 partner)</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n">
         <v>255.92</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="22" t="n">
         <v>62.32</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="22" t="n">
         <v>262.24</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="22" t="n">
         <v>287.26</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="22" t="n">
         <v>79.23</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="23" t="n">
         <v>946.97</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Nairne</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Nairne (K-1 partner)</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>255.92</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="22" t="n">
         <v>62.32</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="22" t="n">
         <v>262.24</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="22" t="n">
         <v>287.26</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="22" t="n">
         <v>79.23</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="23" t="n">
         <v>946.97</v>
       </c>
     </row>
@@ -2620,7 +2634,7 @@
       <c r="F11" s="6" t="n">
         <v>79.23</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="16" t="n">
         <v>946.97</v>
       </c>
     </row>
@@ -2645,7 +2659,7 @@
       <c r="F12" s="6" t="n">
         <v>-278.48</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="16" t="n">
         <v>761.49</v>
       </c>
     </row>
@@ -2670,7 +2684,7 @@
       <c r="F13" s="6" t="n">
         <v>164.9</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <v>164.9</v>
       </c>
     </row>
@@ -2705,22 +2719,22 @@
           <t>TPA Perf Fees Crystallized (what was OWED)</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="24" t="n">
         <v>15355.51</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="24" t="n">
         <v>12474.75</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="24" t="n">
         <v>51906.99</v>
       </c>
-      <c r="E15" s="22" t="n">
+      <c r="E15" s="24" t="n">
         <v>57074.08999999997</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="24" t="n">
         <v>16211.69</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="24" t="n">
         <v>153023.03</v>
       </c>
     </row>
@@ -2730,22 +2744,22 @@
           <t>DELTA (Owed - Paid; positive = unpaid liability)</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="25" t="n">
         <v>6998.820000000002</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="25" t="n">
         <v>93.58000000000175</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="25" t="n">
         <v>3323.809999999998</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="25" t="n">
         <v>100.3499999999622</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="25" t="n">
         <v>1071.080000000004</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="25" t="n">
         <v>11587.63999999996</v>
       </c>
     </row>
@@ -2821,7 +2835,7 @@
       <c r="C4" s="6" t="n">
         <v>15140.61</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="25" t="n">
         <v>1071.080000000002</v>
       </c>
       <c r="E4" t="inlineStr">

--- a/2025-armada-prime-tech-1099-k1.xlsx
+++ b/2025-armada-prime-tech-1099-k1.xlsx
@@ -14,7 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Consultant Monthly" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GP Expenses" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distributions Ledger" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Op Expenses" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Per-Person" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,8 +75,12 @@
       <i val="1"/>
       <color rgb="00999999"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006400"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +111,18 @@
         <bgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
+        <bgColor rgb="00D5F5E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE6CC"/>
+        <bgColor rgb="00FFE6CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -132,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +183,13 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -853,6 +878,122 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation: TPA-derived vs Internal Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>TPA Source ($)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Internal Source ($)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Delta ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dec 2025 Perf Fees Crystallized</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>16211.69</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>15140.61</v>
+      </c>
+      <c r="D4" s="25" t="n">
+        <v>1071.080000000002</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BEST ONE Dec Consultants tab total</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sum 1099 + 0.5% direct slices = Gross Perf</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>153023.0299999999</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>153023.03</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>-2.91038304567337e-11</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Internal arithmetic check</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Unmapped investors (no consultant attribution)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>None — every investor mapped successfully.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2778,111 +2919,1138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Reconciliation: TPA-derived vs Internal Sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>TPA Source ($)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Internal Source ($)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Delta ($)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+          <t>Operating Expenses by Vendor &amp; Month (Aug-Dec 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Each vendor on its own row. Source: Costs sections of Distributions ledger (Aug-Nov) + BEST ONE Dec Costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Vendor / Line Item</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>2025 Total</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dec 2025 Perf Fees Crystallized</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>16211.69</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>15140.61</v>
-      </c>
-      <c r="D4" s="25" t="n">
-        <v>1071.080000000002</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>BEST ONE Dec Consultants tab total</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sum 1099 + 0.5% direct slices = Gross Perf</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>153023.0299999999</v>
+          <t>506c SPV Loan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Loan/SPV</t>
+        </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>153023.03</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>-2.91038304567337e-11</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Internal arithmetic check</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+        <v>4275</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>29275</v>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>RECLASS: likely balance sheet item (loan/capital), not P&amp;L expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>RECLASS: likely annual D&amp;O — pro-rate to ~$7,500 for Aug-Dec</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Unmapped investors (no consultant attribution)</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PVD (verify)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>Vendor identification needed for 1099 obligation</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>None — every investor mapped successfully.</t>
-        </is>
-      </c>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Payroll/Contractor</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>11500</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>Payroll/contractor — likely 1099 (already on consultant 1099 list?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Marketing/Web</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>Marketing/web build</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ad Spend</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Marketing/Ads</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>Marketing — vendor breakdown needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TPA (second line)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Admin / TPA Fee</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>VERIFY: second TPA line in Dec — separate billing or duplicate?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Alpha Verification</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Verification/Compliance</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>2250</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>2250</v>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>Compliance/verification service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Formidium (TPA)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Admin / TPA Fee</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>VERIFY: same as 'TPA (Formidium)' — TPA fee. Confirm GP-paid vs fund-paid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TPA (Formidium)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Admin / TPA Fee</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>VERIFY: $600/mo also in fund-level admin (TPA books). May double-count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>MONTHLY TOTAL</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="12" t="n">
+        <v>10275</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>43500</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>10350</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>27100</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>91225</v>
+      </c>
+      <c r="I15" s="11" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>Likely-adjusted (after accountant reclass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: 506c SPV Loans (balance sheet)</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-29275</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: Insurance proration ($18k → $7,500 for 5 mo)</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-10500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>ADJUSTED 2025 OP EXPENSES</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="28" t="n">
+        <v>51450</v>
+      </c>
+      <c r="I20" s="27" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Per-Person Cash Distributions by Month, with Running YTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Each person: top row = monthly amount paid; bottom row = running YTD total. K-1 partners (Nairne, Raj) shaded blue. Per Nairne 2026-04-30: payouts shown ARE net (after costs + weighted costs). TruQuant excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Person / Recipient</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>YE 2025 Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — Fund Mgmt 59.5% (Aug: 5.5%)</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="n">
+        <v>2815.16</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <v>2815.16</v>
+      </c>
+      <c r="E5" s="22" t="n">
+        <v>7415.62</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <v>10230.78</v>
+      </c>
+      <c r="G5" s="22" t="n">
+        <v>31206.94</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>41437.72</v>
+      </c>
+      <c r="I5" s="22" t="n">
+        <v>34183.9</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <v>75621.62</v>
+      </c>
+      <c r="K5" s="22" t="n">
+        <v>9428.24</v>
+      </c>
+      <c r="L5" s="29" t="n">
+        <v>85049.86</v>
+      </c>
+      <c r="M5" s="23" t="n">
+        <v>85049.86</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>318.24</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>580.48</v>
+      </c>
+      <c r="I6" s="22" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="J6" s="29" t="n">
+        <v>867.74</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="L6" s="29" t="n">
+        <v>946.97</v>
+      </c>
+      <c r="M6" s="23" t="n">
+        <v>946.97</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Raj Duggal — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="E7" s="22" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>318.24</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>580.48</v>
+      </c>
+      <c r="I7" s="22" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="J7" s="29" t="n">
+        <v>867.74</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="L7" s="29" t="n">
+        <v>946.97</v>
+      </c>
+      <c r="M7" s="23" t="n">
+        <v>946.97</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>3172.12</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>3172.12</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>3561.92</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>6734.04</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>11848.88</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>18582.92</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>15124.18</v>
+      </c>
+      <c r="J8" s="30" t="n">
+        <v>33707.1</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>4369.77</v>
+      </c>
+      <c r="L8" s="30" t="n">
+        <v>38076.87</v>
+      </c>
+      <c r="M8" s="16" t="n">
+        <v>38076.87</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1266.18</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>1266.18</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>930.9</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>2197.08</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>3218.29</v>
+      </c>
+      <c r="H9" s="30" t="n">
+        <v>5415.37</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>4184.51</v>
+      </c>
+      <c r="J9" s="30" t="n">
+        <v>9599.880000000001</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>788.78</v>
+      </c>
+      <c r="L9" s="30" t="n">
+        <v>10388.66</v>
+      </c>
+      <c r="M9" s="16" t="n">
+        <v>10388.66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>335.47</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>335.47</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>285.77</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>621.24</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1268.23</v>
+      </c>
+      <c r="H10" s="30" t="n">
+        <v>1889.47</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1833.52</v>
+      </c>
+      <c r="J10" s="30" t="n">
+        <v>3722.99</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>429.71</v>
+      </c>
+      <c r="L10" s="30" t="n">
+        <v>4152.7</v>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>4152.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Phil</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>318.24</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="H11" s="30" t="n">
+        <v>580.48</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="J11" s="30" t="n">
+        <v>867.74</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="L11" s="30" t="n">
+        <v>946.97</v>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>946.97</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Issac</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>254.12</v>
+      </c>
+      <c r="H12" s="30" t="n">
+        <v>254.12</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>785.85</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <v>1039.97</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>-278.48</v>
+      </c>
+      <c r="L12" s="30" t="n">
+        <v>761.49</v>
+      </c>
+      <c r="M12" s="16" t="n">
+        <v>761.49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="M13" s="16" t="n">
+        <v>164.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>K-1 SUBTOTAL (Nairne + Raj)</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>3327</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>3327</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>7540.259999999999</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>10867.26</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>31731.42</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>42598.68</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>34758.42000000001</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>77357.10000000001</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>9586.699999999999</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>86943.8</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>86943.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>1099 SUBTOTAL (Phil + consultants)</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>5029.690000000001</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>5029.690000000001</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>4840.91</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>9870.6</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>16851.76</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>26722.36</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>22215.32</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>48937.68</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>5553.91</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>54491.59</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>54491.59</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr"/>
+      <c r="C16" s="32" t="n">
+        <v>8356.690000000001</v>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>8356.690000000001</v>
+      </c>
+      <c r="E16" s="32" t="n">
+        <v>12381.17</v>
+      </c>
+      <c r="F16" s="32" t="n">
+        <v>20737.86</v>
+      </c>
+      <c r="G16" s="32" t="n">
+        <v>48583.18</v>
+      </c>
+      <c r="H16" s="32" t="n">
+        <v>69321.04000000001</v>
+      </c>
+      <c r="I16" s="32" t="n">
+        <v>56973.74000000001</v>
+      </c>
+      <c r="J16" s="32" t="n">
+        <v>126294.78</v>
+      </c>
+      <c r="K16" s="32" t="n">
+        <v>15140.61</v>
+      </c>
+      <c r="L16" s="32" t="n">
+        <v>141435.39</v>
+      </c>
+      <c r="M16" s="32" t="n">
+        <v>141435.39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>TPA Perf Fees Crystallized (Gross GP Income)</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="24" t="n">
+        <v>15355.51</v>
+      </c>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="24" t="n">
+        <v>12474.75</v>
+      </c>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="24" t="n">
+        <v>51906.99</v>
+      </c>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="24" t="n">
+        <v>57074.08999999997</v>
+      </c>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="24" t="n">
+        <v>16211.69</v>
+      </c>
+      <c r="L17" s="10" t="n"/>
+      <c r="M17" s="24" t="n">
+        <v>153023.03</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Op Expenses (paid from GP retained)</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="24" t="n">
+        <v>10275</v>
+      </c>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="24" t="n">
+        <v>43500</v>
+      </c>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="24" t="n">
+        <v>10350</v>
+      </c>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="24" t="n">
+        <v>27100</v>
+      </c>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="24" t="n">
+        <v>91225</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="35" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Payouts shown are NET — already after weighted costs (per Nairne 2026-04-30). The Distributions ledger's separate 'Gross vs Net' table tracks cumulative settlement balances (carries forward unpaid amounts) and a layer of Coinbase/wire/Crypto fees (~2.8%) plus per-person 'Expense' allocations (Nairne Expense, Alec Expense, etc.) — those are nested inside the Net amounts you see here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="35" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>TruQuant payments are excluded entirely (per Nairne 2026-04-30). The Aug TruQuant amounts ($6,909.93 Trader &amp; Developer + $88.78 Spydr) and Sep Spydr $82.08 are NOT in any of the rows above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="35" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Aug 2025 used a different waterfall (Fund Mgmt was 5.5% not 59.5%). From Sep onwards: standard 59.5% Mgmt + 39% Consultant + 0.5%×3 principals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="35" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Issac shows -$278.48 in Dec — clawback against prior month overpayment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="35" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Op Expenses row at the bottom is the GP-paid vendor expenses (not allocated to individuals on this tab — see Monthly Op Expenses tab for vendor breakdown).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/2025-armada-prime-tech-1099-k1.xlsx
+++ b/2025-armada-prime-tech-1099-k1.xlsx
@@ -16,7 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distributions Ledger" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Op Expenses" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Per-Person" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aug 2025 Detail" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sep 2025 Detail" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oct 2025 Detail" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nov 2025 Detail" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dec 2025 Detail" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,6 +83,10 @@
     <font>
       <b val="1"/>
       <color rgb="00006400"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="8">
@@ -150,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,6 +199,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -884,6 +897,2503 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Aug 2025 — GP P&amp;L Detail (Armada Prime Tech LLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>AUGUST SPECIAL WATERFALL: 9.5% Consultant + 13.5% Trader &amp; Developer (TQ-excluded) + 5.5% Mgmt + 0.5%×3 principals = 30% of true gross. TruQuant moved upstream from Sep onwards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>CAPITAL IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fund Total Income (Armada Prime LLP, 82% post-TQ)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>51360.02</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>15355.51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>PAID OUT — K-1 PARTNERS (Nairne 60% + Raj 0.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Recipient</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Gross Slice</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Net Paid</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — Fund Mgmt 5.5% slice</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>2815.16</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>2815.16</v>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Nairne's share of GP cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Raj Duggal — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>K-1 Subtotal</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="n">
+        <v>3327</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>3327</v>
+      </c>
+      <c r="E13" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>PAID OUT — 1099 CONTRACTORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Recipient</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Gross Slice</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Net Paid</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>3172.12</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>3172.12</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>9.5% × his investors' gross profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1266.18</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1266.18</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>9.5% × his investors' gross profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>335.47</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>335.47</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>9.5% × her investors' gross profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Phil</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.5% direct slice (1099, not K-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>1099 Subtotal</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="8" t="n">
+        <v>5029.690000000001</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>5029.690000000001</v>
+      </c>
+      <c r="E21" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>8356.690000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES (paid by GP entity to vendors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>506c SPV Loan</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Loan/SPV</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>4275</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RECLASS: likely balance sheet, not P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PVD (verify)</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Op Expenses Subtotal</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="8" t="n">
+        <v>10275</v>
+      </c>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>RECONCILIATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Capital In (TPA Perf Fees Crystallized)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>15355.51</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Less: Cash to people (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-8356.690000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Less: Op expenses to vendors</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>-10275</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7">
+        <f> Residual / (Deficit) for the month</f>
+        <v/>
+      </c>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="34" t="n"/>
+      <c r="D35" s="35" t="n">
+        <v>-3276.179999999998</v>
+      </c>
+      <c r="E35" s="34" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>AUG NOTES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>TruQuant payments excluded: $6,909.93 'Trader &amp; Developer' (13.5%) + $88.78 Spydr — total $6,998.71. These are upstream of the GP entity per Nairne 2026-04-30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>If you ADD BACK the $6,998.71 TQ-excluded amounts, total cash flow ties to the full $15,355.51 GP cut: $8,356.69 (people) + $6,998.71 (TQ) = $15,355.40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Op expenses ($10,275 SPV+PVD) are funded out of GP retained earnings, NOT from people's slices.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A40:E40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sep 2025 — GP P&amp;L Detail (Armada Prime Tech LLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Standard waterfall: 59.5% Fund Mgmt (Nairne K-1) + 39% Consultant + 0.5%×3 principals = 30% of fund net.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>CAPITAL IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fund Total Income (Armada Prime LLP, 82% post-TQ)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>74798.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>12474.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>PAID OUT — K-1 PARTNERS (Nairne 60% + Raj 0.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Recipient</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Gross Slice</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Net Paid</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — Fund Mgmt 59.5% slice</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>7415.62</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>7415.62</v>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Nairne's share of GP cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Raj Duggal — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>K-1 Subtotal</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="n">
+        <v>7540.259999999999</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>7540.259999999999</v>
+      </c>
+      <c r="E13" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>PAID OUT — 1099 CONTRACTORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Recipient</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Gross Slice</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Net Paid</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>3561.92</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>3561.92</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>930.9</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>930.9</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>285.77</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>285.77</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>39% × her investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Phil</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.5% direct slice (1099, not K-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>1099 Subtotal</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="8" t="n">
+        <v>4840.91</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>4840.91</v>
+      </c>
+      <c r="E21" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>12381.17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES (paid by GP entity to vendors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>(no GP-paid op expenses recorded for this month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Op Expenses Subtotal</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>RECONCILIATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Capital In (TPA Perf Fees Crystallized)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>12474.75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Less: Cash to people (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-12381.17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Less: Op expenses to vendors</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7">
+        <f> Residual / (Deficit) for the month</f>
+        <v/>
+      </c>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="34" t="n"/>
+      <c r="D34" s="36" t="n">
+        <v>93.58000000000357</v>
+      </c>
+      <c r="E34" s="34" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Oct 2025 — GP P&amp;L Detail (Armada Prime Tech LLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Standard waterfall: 59.5% Fund Mgmt (Nairne K-1) + 39% Consultant + 0.5%×3 principals = 30% of fund net.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>CAPITAL IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fund Total Income (Armada Prime LLP, 82% post-TQ)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>173713.66</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>51906.99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>PAID OUT — K-1 PARTNERS (Nairne 60% + Raj 0.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Recipient</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Gross Slice</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Net Paid</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — Fund Mgmt 59.5% slice</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>31206.94</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>31206.94</v>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Nairne's share of GP cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Raj Duggal — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>K-1 Subtotal</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="n">
+        <v>31731.42</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>31731.42</v>
+      </c>
+      <c r="E13" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>PAID OUT — 1099 CONTRACTORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Recipient</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Gross Slice</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Net Paid</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>11848.88</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>11848.88</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>3218.29</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3218.29</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1268.23</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1268.23</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>39% × her investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Phil</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.5% direct slice (1099, not K-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Issac</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>254.12</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>254.12</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>1099 Subtotal</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="8" t="n">
+        <v>16851.76</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>16851.76</v>
+      </c>
+      <c r="E22" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>48583.18</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES (paid by GP entity to vendors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>506c SPV Loan</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Loan/SPV</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RECLASS: likely balance sheet, not P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PVD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PVD (verify)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Marketing/Web</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ad Spend</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Marketing/Ads</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Op Expenses Subtotal</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="8" t="n">
+        <v>43500</v>
+      </c>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
+        <is>
+          <t>RECONCILIATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Capital In (TPA Perf Fees Crystallized)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>51906.99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Less: Cash to people (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>-48583.18</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Less: Op expenses to vendors</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>-43500</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7">
+        <f> Residual / (Deficit) for the month</f>
+        <v/>
+      </c>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="34" t="n"/>
+      <c r="D38" s="35" t="n">
+        <v>-40176.19</v>
+      </c>
+      <c r="E38" s="34" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nov 2025 — GP P&amp;L Detail (Armada Prime Tech LLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Standard waterfall: 59.5% Fund Mgmt (Nairne K-1) + 39% Consultant + 0.5%×3 principals = 30% of fund net.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>CAPITAL IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fund Total Income (Armada Prime LLP, 82% post-TQ)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>190568.39</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>57074.08999999997</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>PAID OUT — K-1 PARTNERS (Nairne 60% + Raj 0.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Recipient</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Gross Slice</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Net Paid</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — Fund Mgmt 59.5% slice</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>34183.9</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>34183.9</v>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Nairne's share of GP cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Raj Duggal — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>K-1 Subtotal</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="n">
+        <v>34758.42000000001</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>34758.42000000001</v>
+      </c>
+      <c r="E13" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>PAID OUT — 1099 CONTRACTORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Recipient</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Gross Slice</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Net Paid</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>15124.18</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>15124.18</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>4184.51</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>4184.51</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1833.52</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1833.52</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>39% × her investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Issac</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>785.85</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>785.85</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Phil</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.5% direct slice (1099, not K-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>1099 Subtotal</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="8" t="n">
+        <v>22215.32</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>22215.32</v>
+      </c>
+      <c r="E22" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>56973.74000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES (paid by GP entity to vendors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Payroll/Contractor</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Alpha Verification</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Verification/Compliance</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Formidium (TPA)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Admin / TPA Fee</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>VERIFY GP-paid vs fund-paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Op Expenses Subtotal</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="8" t="n">
+        <v>10350</v>
+      </c>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="33" t="inlineStr">
+        <is>
+          <t>RECONCILIATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Capital In (TPA Perf Fees Crystallized)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>57074.08999999997</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Less: Cash to people (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>-56973.74000000001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Less: Op expenses to vendors</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>-10350</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7">
+        <f> Residual / (Deficit) for the month</f>
+        <v/>
+      </c>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="34" t="n"/>
+      <c r="D37" s="35" t="n">
+        <v>-10249.65000000004</v>
+      </c>
+      <c r="E37" s="34" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Dec 2025 — GP P&amp;L Detail (Armada Prime Tech LLC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Standard waterfall: 59.5% Fund Mgmt (Nairne K-1) + 39% Consultant + 0.5%×3 principals = 30% of fund net.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>CAPITAL IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fund Total Income (Armada Prime LLP, 82% post-TQ)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>100636.99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>16211.69</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>PAID OUT — K-1 PARTNERS (Nairne 60% + Raj 0.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Recipient</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Gross Slice</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Net Paid</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — Fund Mgmt 59.5% slice</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>9428.24</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>9428.24</v>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Nairne's share of GP cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Nairne — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Raj Duggal — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>K-1 Subtotal</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="8" t="n">
+        <v>9586.699999999999</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>9586.699999999999</v>
+      </c>
+      <c r="E13" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>PAID OUT — 1099 CONTRACTORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Recipient</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Tax Type</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Gross Slice</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Net Paid</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>4369.77</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>4369.77</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>788.78</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>788.78</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>429.71</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>429.71</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>39% × her investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Phil</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.5% direct slice (1099, not K-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Issac</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>-278.48</v>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>-278.48</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>39% × his investors' perf fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>1099 Subtotal</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="8" t="n">
+        <v>5553.91</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>5553.91</v>
+      </c>
+      <c r="E23" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>15140.61</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSES (paid by GP entity to vendors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Payroll/Contractor</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TPA (Formidium)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Admin / TPA Fee</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>VERIFY GP-paid vs fund-paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RECLASS: likely annual D&amp;O, pro-rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TPA (second line)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Admin / TPA Fee</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VERIFY GP-paid vs fund-paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Op Expenses Subtotal</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="8" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>RECONCILIATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Capital In (TPA Perf Fees Crystallized)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>16211.69</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Less: Cash to people (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>-15140.61</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Less: Op expenses to vendors</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>-27100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7">
+        <f> Residual / (Deficit) for the month</f>
+        <v/>
+      </c>
+      <c r="B39" s="34" t="n"/>
+      <c r="C39" s="34" t="n"/>
+      <c r="D39" s="35" t="n">
+        <v>-26028.92</v>
+      </c>
+      <c r="E39" s="34" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/2025-armada-prime-tech-1099-k1.xlsx
+++ b/2025-armada-prime-tech-1099-k1.xlsx
@@ -667,7 +667,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>LESS: 1099 EXPENSES (contractor payments — partners excluded)</t>
+          <t>LESS: 1099 EXPENSES (contractor payments — K-1 partners excluded)</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -689,139 +689,139 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Phil (0.5% GP fixed slice)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>946.97</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Phil held the 0.5% slice in 2025 as a 1099 contractor</t>
-        </is>
-      </c>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOTAL 1099 EXPENSES</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>53544.62</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOTAL 1099 EXPENSES</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>54491.59</v>
-      </c>
-      <c r="C13" s="7" t="inlineStr"/>
+      <c r="A13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>LESS: GP-PAID OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>LESS: GP-PAID OPERATING EXPENSES</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Vendor expenses (Chris, Insurance, PVD, Website, etc.)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>91225</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>See GP Expenses tab. Includes items likely needing reclass (SPV loans → balance sheet, Insurance pro-rata).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Vendor expenses (Chris, Insurance, PVD, Website, etc.)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>91225</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>See GP Expenses tab. Includes items likely needing reclass (SPV loans → balance sheet, Insurance pro-rata).</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PARTNERSHIP NET INCOME (allocated to K-1 partners)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>8253.409999999974</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gross - 1099 expenses - Op expenses. This is what flows to K-1s.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PARTNERSHIP NET INCOME (allocated to K-1 partners)</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>7306.439999999973</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Gross - 1099 expenses - Op expenses. This is what flows to K-1s.</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>K-1 ALLOCATION (per ownership: Nairne 60% / Raj 0.5% / Phil 0.5%)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>K-1 ALLOCATION (per ownership: Nairne 60% / Raj 0.5%)</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Nairne — Fund Mgmt 59.5% slice received as cash</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>85049.86</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Reported as K-1 income (partner allocation, not expense)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Nairne — Fund Mgmt 59.5% slice received as cash</t>
+          <t xml:space="preserve">  Nairne — direct 0.5% slice received as cash</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>85049.86</v>
+        <v>946.97</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Reported as K-1 income (partner allocation, not expense)</t>
+          <t>Reported as K-1 income</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Nairne — direct 0.5% slice received as cash</t>
+          <t xml:space="preserve">  Nairne — TOTAL cash received (60% of perf fees)</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>946.97</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Reported as K-1 income</t>
-        </is>
+        <v>85996.83</v>
+      </c>
+      <c r="C22">
+        <f> Fund Mgmt + direct slice</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Nairne — TOTAL cash received (60% of perf fees)</t>
+          <t xml:space="preserve">  Raj — direct 0.5% slice received as cash</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>85996.83</v>
-      </c>
-      <c r="C23">
-        <f> Fund Mgmt + direct slice</f>
-        <v/>
+        <v>946.97</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Reported as K-1 income</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Raj — direct 0.5% slice received as cash</t>
+          <t xml:space="preserve">  Phil — direct 0.5% slice received as cash</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
@@ -829,7 +829,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Reported as K-1 income</t>
+          <t>Reported as K-1 income (Phil corrected to K-1 partner per Nairne 2026-05-05)</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Total cash out (1099s $54,491.59 + Nairne K-1 $85,996.83 + Raj K-1 $946.97)</t>
+          <t>Total cash out (1099s $53,544.62 + Nairne K-1 $85,996.83 + Raj K-1 $946.97 + Phil K-1 $946.97)</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
@@ -1052,81 +1052,81 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Phil — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>K-1 Subtotal</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="n">
-        <v>3327</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>3327</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="n">
+        <v>3582.92</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>3582.92</v>
+      </c>
+      <c r="E14" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>PAID OUT — 1099 CONTRACTORS</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Recipient</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Tax Type</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Gross Slice</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Net Paid</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alec Atkinson</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>3172.12</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>3172.12</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>9.5% × his investors' gross profit</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1266.18</v>
+        <v>3172.12</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1266.18</v>
+        <v>3172.12</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1158,21 +1158,21 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>335.47</v>
+        <v>1266.18</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>335.47</v>
+        <v>1266.18</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9.5% × her investors' gross profit</t>
+          <t>9.5% × his investors' gross profit</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1181,14 +1181,14 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>255.92</v>
+        <v>335.47</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>255.92</v>
+        <v>335.47</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.5% direct slice (1099, not K-1)</t>
+          <t>9.5% × her investors' gross profit</t>
         </is>
       </c>
     </row>
@@ -1200,10 +1200,10 @@
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="8" t="n">
-        <v>5029.690000000001</v>
+        <v>4773.77</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>5029.690000000001</v>
+        <v>4773.77</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1546,81 +1546,81 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Phil — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>K-1 Subtotal</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="n">
-        <v>7540.259999999999</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>7540.259999999999</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="n">
+        <v>7602.579999999999</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>7602.579999999999</v>
+      </c>
+      <c r="E14" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>PAID OUT — 1099 CONTRACTORS</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Recipient</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Tax Type</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Gross Slice</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Net Paid</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alec Atkinson</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>3561.92</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>3561.92</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>930.9</v>
+        <v>3561.92</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>930.9</v>
+        <v>3561.92</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>285.77</v>
+        <v>930.9</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>285.77</v>
+        <v>930.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39% × her investors' perf fees</t>
+          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1675,14 +1675,14 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>62.32</v>
+        <v>285.77</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>62.32</v>
+        <v>285.77</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.5% direct slice (1099, not K-1)</t>
+          <t>39% × her investors' perf fees</t>
         </is>
       </c>
     </row>
@@ -1694,10 +1694,10 @@
       </c>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="8" t="n">
-        <v>4840.91</v>
+        <v>4778.59</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>4840.91</v>
+        <v>4778.59</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1980,81 +1980,81 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Phil — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>K-1 Subtotal</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="n">
-        <v>31731.42</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>31731.42</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="n">
+        <v>31993.66</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>31993.66</v>
+      </c>
+      <c r="E14" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>PAID OUT — 1099 CONTRACTORS</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Recipient</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Tax Type</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Gross Slice</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Net Paid</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alec Atkinson</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>11848.88</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>11848.88</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3218.29</v>
+        <v>11848.88</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>3218.29</v>
+        <v>11848.88</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>1268.23</v>
+        <v>3218.29</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1268.23</v>
+        <v>3218.29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39% × her investors' perf fees</t>
+          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2109,14 +2109,14 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>262.24</v>
+        <v>1268.23</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>262.24</v>
+        <v>1268.23</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.5% direct slice (1099, not K-1)</t>
+          <t>39% × her investors' perf fees</t>
         </is>
       </c>
     </row>
@@ -2151,10 +2151,10 @@
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="8" t="n">
-        <v>16851.76</v>
+        <v>16589.52</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>16851.76</v>
+        <v>16589.52</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -2498,81 +2498,81 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Phil — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>K-1 Subtotal</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="n">
-        <v>34758.42000000001</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>34758.42000000001</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="n">
+        <v>35045.68000000001</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>35045.68000000001</v>
+      </c>
+      <c r="E14" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>PAID OUT — 1099 CONTRACTORS</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Recipient</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Tax Type</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Gross Slice</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Net Paid</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alec Atkinson</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>15124.18</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>15124.18</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>4184.51</v>
+        <v>15124.18</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>4184.51</v>
+        <v>15124.18</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2604,21 +2604,21 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>1833.52</v>
+        <v>4184.51</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1833.52</v>
+        <v>4184.51</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39% × her investors' perf fees</t>
+          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>785.85</v>
+        <v>1833.52</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>785.85</v>
+        <v>1833.52</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39% × his investors' perf fees</t>
+          <t>39% × her investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Issac</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2650,14 +2650,14 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>287.26</v>
+        <v>785.85</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>287.26</v>
+        <v>785.85</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.5% direct slice (1099, not K-1)</t>
+          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
@@ -2669,10 +2669,10 @@
       </c>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="8" t="n">
-        <v>22215.32</v>
+        <v>21928.06</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>22215.32</v>
+        <v>21928.06</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -3000,81 +3000,81 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Phil — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>K-1 Subtotal</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="n">
-        <v>9586.699999999999</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>9586.699999999999</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="n">
+        <v>9665.929999999998</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>9665.929999999998</v>
+      </c>
+      <c r="E14" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>PAID OUT — 1099 CONTRACTORS</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Recipient</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Tax Type</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Gross Slice</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Net Paid</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alec Atkinson</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>4369.77</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>4369.77</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>788.78</v>
+        <v>4369.77</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>788.78</v>
+        <v>4369.77</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>429.71</v>
+        <v>788.78</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>429.71</v>
+        <v>788.78</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39% × her investors' perf fees</t>
+          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3129,21 +3129,21 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>164.9</v>
+        <v>429.71</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>164.9</v>
+        <v>429.71</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39% × his investors' perf fees</t>
+          <t>39% × her investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3152,14 +3152,14 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>79.23</v>
+        <v>164.9</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>79.23</v>
+        <v>164.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.5% direct slice (1099, not K-1)</t>
+          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
@@ -3194,10 +3194,10 @@
       </c>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="8" t="n">
-        <v>5553.91</v>
+        <v>5474.68</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>5553.91</v>
+        <v>5474.68</v>
       </c>
       <c r="E23" s="7" t="n"/>
     </row>
@@ -3510,7 +3510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3571,11 +3571,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Phil (last name TBD)</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>946.97</v>
+        <v>38076.87</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5% GP fixed slice (held by Phil all 2025)</t>
+          <t>From Distributions ledger (cash actually paid)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -3593,11 +3593,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>38076.87</v>
+        <v>10388.66</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3615,11 +3615,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>10388.66</v>
+        <v>4152.7</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3637,11 +3637,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Issac</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>4152.7</v>
+        <v>761.49</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3659,11 +3659,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>761.49</v>
+        <v>164.9</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3679,53 +3679,31 @@
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Luke</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>164.9</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Individual 1099</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>From Distributions ledger (cash actually paid)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>TOTAL 1099 PAYMENTS</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>54491.59</v>
-      </c>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-    </row>
-    <row r="12"/>
+      <c r="B10" s="12" t="n">
+        <v>53544.62</v>
+      </c>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>K-1 partner cash distributions (NOT on 1099s): Nairne $85,996.83 + Raj $946.97 = $86,943.80</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>K-1 partner cash distributions (NOT on 1099s): Nairne $85,996.83 + Raj $946.97 = $86,943.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Cross-check: 1099 total ($54,491.59) + K-1 cash ($86,943.80) = $141,435.39; Gross perf fees per TPA = $153,023.03; delta = $11,587.64 (cash-vs-accrual timing + Aug TQ-T&amp;D excluded)</t>
+          <t>Cross-check: 1099 total ($53,544.62) + K-1 cash ($86,943.80) = $140,488.42; Gross perf fees per TPA = $153,023.03; delta = $12,534.61 (cash-vs-accrual timing + Aug TQ-T&amp;D excluded)</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3764,7 +3742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Members per Nairne 2026-04-30: Nairne (60% — Fund Mgmt 59.5% + direct 0.5%) and Raj Duggal (0.5%). Net income allocated per the operating agreement.</t>
+          <t>Members per Nairne 2026-05-05: Nairne (60% — Fund Mgmt 59.5% + direct 0.5%), Raj Duggal (0.5%), and Phil (0.5%). Net income allocated per the operating agreement.</t>
         </is>
       </c>
     </row>
@@ -3804,14 +3782,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99.17%</t>
+          <t>98.36%</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
         <v>85996.83</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>7246.056198347081</v>
+        <v>8118.108196721286</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -3823,132 +3801,159 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
         <v>946.97</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>60.38380165289234</v>
+        <v>67.65090163934406</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Phil</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.82%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>946.97</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>67.65090163934406</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>K-1 ARITHMETIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GP Gross Income (TPA Perf Fees Crystallized): $153,023.03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Less: 1099 contractor expenses (Alec/Jake/AJ/Phil/Issac/Luke): $54,491.59</t>
+          <t>GP Gross Income (TPA Perf Fees Crystallized): $153,023.03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Less: 1099 contractor expenses (Alec/Jake/AJ/Issac/Luke): $53,544.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Less: GP-paid operating expenses: $91,225.00</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12">
-        <f> Partnership NET INCOME (allocated to K-1s): $7,306.44</f>
+    <row r="13">
+      <c r="A13">
+        <f> Partnership NET INCOME (allocated to K-1s): $8,253.41</f>
         <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Nairne allocated share (99.17%): $7,246.06</t>
-        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Raj allocated share (0.83%): $60.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>Nairne allocated share (98.36%): $8,118.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Raj allocated share (0.82%): $67.65</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Phil allocated share (0.82%): $67.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Fund Mgmt 59.5% slice is Nairne's K-1 income (per Nairne 2026-04-30 — it's not a separate entity 1099).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Cash distributions and allocated K-1 net income are different things in partnership tax — Schedule K-1 reports both. The accountant will compute capital account changes.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Operating expenses include items that may be reclassed by the accountant (506c SPV Loans → balance sheet; Insurance $18k may need annual proration).</t>
+          <t>Fund Mgmt 59.5% slice is Nairne's K-1 income (per Nairne 2026-04-30 — it's not a separate entity 1099).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Cash-basis 1099s (above) may differ from accrual-basis (TPA-derived). Confirm GP's tax basis with accountant.</t>
+          <t>Cash distributions and allocated K-1 net income are different things in partnership tax — Schedule K-1 reports both. The accountant will compute capital account changes.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>TruQuant payments are excluded per Nairne 2026-04-30 (TQ is not a GP expense).</t>
+          <t>Operating expenses include items that may be reclassed by the accountant (506c SPV Loans → balance sheet; Insurance $18k may need annual proration).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Ownership % shown (Nairne 99.17%/Raj 0.83%) is derived from the 60/0.5 split. The actual LLC operating agreement governs — confirm with the accountant before filing.</t>
+          <t>Cash-basis 1099s (above) may differ from accrual-basis (TPA-derived). Confirm GP's tax basis with accountant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>TruQuant payments are excluded per Nairne 2026-04-30 (TQ is not a GP expense).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Ownership % shown (Nairne 98.36%/Raj 0.82%/Phil 0.82%) is derived from the 60/0.5/0.5 split. The actual LLC operating agreement governs — confirm with the accountant before filing.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5265,27 +5270,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Phil</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Phil (K-1 partner)</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
         <v>255.92</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="22" t="n">
         <v>62.32</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="22" t="n">
         <v>262.24</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="22" t="n">
         <v>287.26</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="22" t="n">
         <v>79.23</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="23" t="n">
         <v>946.97</v>
       </c>
     </row>
@@ -6067,54 +6072,54 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Alec Atkinson</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>3172.12</v>
-      </c>
-      <c r="D8" s="30" t="n">
-        <v>3172.12</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>3561.92</v>
-      </c>
-      <c r="F8" s="30" t="n">
-        <v>6734.04</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>11848.88</v>
-      </c>
-      <c r="H8" s="30" t="n">
-        <v>18582.92</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>15124.18</v>
-      </c>
-      <c r="J8" s="30" t="n">
-        <v>33707.1</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>4369.77</v>
-      </c>
-      <c r="L8" s="30" t="n">
-        <v>38076.87</v>
-      </c>
-      <c r="M8" s="16" t="n">
-        <v>38076.87</v>
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Phil — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>318.24</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>580.48</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>867.74</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="L8" s="29" t="n">
+        <v>946.97</v>
+      </c>
+      <c r="M8" s="23" t="n">
+        <v>946.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6123,43 +6128,43 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>1266.18</v>
+        <v>3172.12</v>
       </c>
       <c r="D9" s="30" t="n">
-        <v>1266.18</v>
+        <v>3172.12</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>930.9</v>
+        <v>3561.92</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>2197.08</v>
+        <v>6734.04</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>3218.29</v>
+        <v>11848.88</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>5415.37</v>
+        <v>18582.92</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>4184.51</v>
+        <v>15124.18</v>
       </c>
       <c r="J9" s="30" t="n">
-        <v>9599.880000000001</v>
+        <v>33707.1</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>788.78</v>
+        <v>4369.77</v>
       </c>
       <c r="L9" s="30" t="n">
-        <v>10388.66</v>
+        <v>38076.87</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>10388.66</v>
+        <v>38076.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6168,43 +6173,43 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>335.47</v>
+        <v>1266.18</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>335.47</v>
+        <v>1266.18</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>285.77</v>
+        <v>930.9</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>621.24</v>
+        <v>2197.08</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>1268.23</v>
+        <v>3218.29</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>1889.47</v>
+        <v>5415.37</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1833.52</v>
+        <v>4184.51</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>3722.99</v>
+        <v>9599.880000000001</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>429.71</v>
+        <v>788.78</v>
       </c>
       <c r="L10" s="30" t="n">
-        <v>4152.7</v>
+        <v>10388.66</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>4152.7</v>
+        <v>10388.66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6213,37 +6218,37 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>255.92</v>
+        <v>335.47</v>
       </c>
       <c r="D11" s="30" t="n">
-        <v>255.92</v>
+        <v>335.47</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>62.32</v>
+        <v>285.77</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>318.24</v>
+        <v>621.24</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>262.24</v>
+        <v>1268.23</v>
       </c>
       <c r="H11" s="30" t="n">
-        <v>580.48</v>
+        <v>1889.47</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>287.26</v>
+        <v>1833.52</v>
       </c>
       <c r="J11" s="30" t="n">
-        <v>867.74</v>
+        <v>3722.99</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>79.23</v>
+        <v>429.71</v>
       </c>
       <c r="L11" s="30" t="n">
-        <v>946.97</v>
+        <v>4152.7</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>946.97</v>
+        <v>4152.7</v>
       </c>
     </row>
     <row r="12">
@@ -6321,7 +6326,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>K-1 SUBTOTAL (Nairne + Raj)</t>
+          <t>K-1 SUBTOTAL (Nairne + Raj + Phil)</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -6330,43 +6335,43 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>3327</v>
+        <v>3582.92</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>3327</v>
+        <v>3582.92</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>7540.259999999999</v>
+        <v>7602.579999999999</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>10867.26</v>
+        <v>11185.5</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>31731.42</v>
+        <v>31993.66</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>42598.68</v>
+        <v>43179.16</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>34758.42000000001</v>
+        <v>35045.68000000001</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>77357.10000000001</v>
+        <v>78224.84000000001</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>9586.699999999999</v>
+        <v>9665.929999999998</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>86943.8</v>
+        <v>87890.77</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>86943.8</v>
+        <v>87890.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>1099 SUBTOTAL (Phil + consultants)</t>
+          <t>1099 SUBTOTAL (consultants only)</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
@@ -6375,37 +6380,37 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>5029.690000000001</v>
+        <v>4773.77</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>5029.690000000001</v>
+        <v>4773.77</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>4840.91</v>
+        <v>4778.59</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>9870.6</v>
+        <v>9552.360000000001</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>16851.76</v>
+        <v>16589.52</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>26722.36</v>
+        <v>26141.88</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>22215.32</v>
+        <v>21928.06</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>48937.68</v>
+        <v>48069.94</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>5553.91</v>
+        <v>5474.68</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>54491.59</v>
+        <v>53544.62</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>54491.59</v>
+        <v>53544.62</v>
       </c>
     </row>
     <row r="16">

--- a/2025-armada-prime-tech-1099-k1.xlsx
+++ b/2025-armada-prime-tech-1099-k1.xlsx
@@ -159,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,6 +175,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -191,7 +192,6 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,7 +202,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -680,7 +679,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>53544.62</v>
+        <v>86531.81</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -695,7 +694,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>53544.62</v>
+        <v>86531.81</v>
       </c>
       <c r="C12" s="7" t="inlineStr"/>
     </row>
@@ -738,7 +737,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>8253.409999999974</v>
+        <v>-24733.78000000003</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -766,7 +765,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>85049.86</v>
+        <v>0</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -781,7 +780,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>946.97</v>
+        <v>34188.88</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -796,7 +795,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>85996.83</v>
+        <v>34188.88</v>
       </c>
       <c r="C22">
         <f> Fund Mgmt + direct slice</f>
@@ -860,15 +859,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Total cash out (1099s $53,544.62 + Nairne K-1 $85,996.83 + Raj K-1 $946.97 + Phil K-1 $946.97)</t>
+          <t>Total cash out (1099s $86,531.81 + Nairne K-1 $34,188.88 + Raj K-1 $946.97 + Phil K-1 $946.97)</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>141435.39</v>
+        <v>122614.63</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>vs Gross $153,023.03 — delta $11,587.64 (= retained / cash-vs-accrual / TQ exclusion)</t>
+          <t>vs Gross $153,023.03 — delta $30,408.40 (= retained / cash-vs-accrual / TQ exclusion)</t>
         </is>
       </c>
     </row>
@@ -944,7 +943,7 @@
           <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>15355.51</v>
       </c>
     </row>
@@ -983,92 +982,92 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 5.5% slice</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>2815.16</v>
       </c>
-      <c r="D10" s="22" t="n">
-        <v>2815.16</v>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="D10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>Nairne's share of GP cut</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>255.92</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
+        <v>1663.5</v>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Raj Duggal — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="n">
         <v>255.92</v>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="D12" s="23" t="n">
+        <v>255.92</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Raj Duggal — direct 0.5%</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Phil — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>255.92</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>255.92</v>
       </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Direct member slice</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Phil — direct 0.5%</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>K-1</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>255.92</v>
-      </c>
-      <c r="D13" s="22" t="n">
-        <v>255.92</v>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
         </is>
@@ -1085,7 +1084,7 @@
         <v>3582.92</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3582.92</v>
+        <v>2175.34</v>
       </c>
       <c r="E14" s="7" t="n"/>
     </row>
@@ -1149,7 +1148,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1158,21 +1157,21 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>1266.18</v>
+        <v>335.47</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1266.18</v>
+        <v>1743.04</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9.5% × his investors' gross profit</t>
+          <t>9.5% × her investors' gross profit</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1181,14 +1180,14 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>335.47</v>
+        <v>1266.18</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>335.47</v>
+        <v>1266.18</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9.5% × her investors' gross profit</t>
+          <t>9.5% × his investors' gross profit</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1202,7 @@
         <v>4773.77</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>4773.77</v>
+        <v>6181.34</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1213,8 +1212,8 @@
           <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="n">
-        <v>8356.690000000001</v>
+      <c r="D23" s="17" t="n">
+        <v>8356.68</v>
       </c>
     </row>
     <row r="25">
@@ -1320,7 +1319,7 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>-8356.690000000001</v>
+        <v>-8356.68</v>
       </c>
     </row>
     <row r="34">
@@ -1341,33 +1340,33 @@
       <c r="B35" s="34" t="n"/>
       <c r="C35" s="34" t="n"/>
       <c r="D35" s="35" t="n">
-        <v>-3276.179999999998</v>
+        <v>-3276.169999999998</v>
       </c>
       <c r="E35" s="34" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>AUG NOTES:</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>TruQuant payments excluded: $6,909.93 'Trader &amp; Developer' (13.5%) + $88.78 Spydr — total $6,998.71. These are upstream of the GP entity per Nairne 2026-04-30.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>If you ADD BACK the $6,998.71 TQ-excluded amounts, total cash flow ties to the full $15,355.51 GP cut: $8,356.69 (people) + $6,998.71 (TQ) = $15,355.40.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Op expenses ($10,275 SPV+PVD) are funded out of GP retained earnings, NOT from people's slices.</t>
         </is>
@@ -1438,7 +1437,7 @@
           <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>12474.75</v>
       </c>
     </row>
@@ -1477,92 +1476,92 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 59.5% slice</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>7415.62</v>
       </c>
-      <c r="D10" s="22" t="n">
-        <v>7415.62</v>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="D10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>Nairne's share of GP cut</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>62.32</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
+        <v>5845.12</v>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Raj Duggal — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="n">
         <v>62.32</v>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="D12" s="23" t="n">
+        <v>62.32</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Raj Duggal — direct 0.5%</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Phil — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>62.32</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>62.32</v>
       </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Direct member slice</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Phil — direct 0.5%</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>K-1</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>62.32</v>
-      </c>
-      <c r="D13" s="22" t="n">
-        <v>62.32</v>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
         </is>
@@ -1579,7 +1578,7 @@
         <v>7602.579999999999</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>7602.579999999999</v>
+        <v>5969.759999999999</v>
       </c>
       <c r="E14" s="7" t="n"/>
     </row>
@@ -1620,7 +1619,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1629,21 +1628,21 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>3561.92</v>
+        <v>285.77</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>3561.92</v>
+        <v>6068.58</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>39% × his investors' perf fees</t>
+          <t>39% × her investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1652,10 +1651,10 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>930.9</v>
+        <v>3561.92</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>930.9</v>
+        <v>3561.92</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1666,7 +1665,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1675,14 +1674,14 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>285.77</v>
+        <v>930.9</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>285.77</v>
+        <v>930.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39% × her investors' perf fees</t>
+          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1696,7 @@
         <v>4778.59</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>4778.59</v>
+        <v>10561.4</v>
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
@@ -1707,8 +1706,8 @@
           <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="n">
-        <v>12381.17</v>
+      <c r="D23" s="17" t="n">
+        <v>16531.16</v>
       </c>
     </row>
     <row r="25">
@@ -1742,7 +1741,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>(no GP-paid op expenses recorded for this month)</t>
         </is>
@@ -1785,7 +1784,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-12381.17</v>
+        <v>-16531.16</v>
       </c>
     </row>
     <row r="33">
@@ -1805,8 +1804,8 @@
       </c>
       <c r="B34" s="34" t="n"/>
       <c r="C34" s="34" t="n"/>
-      <c r="D34" s="36" t="n">
-        <v>93.58000000000357</v>
+      <c r="D34" s="35" t="n">
+        <v>-4056.409999999998</v>
       </c>
       <c r="E34" s="34" t="n"/>
     </row>
@@ -1872,7 +1871,7 @@
           <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>51906.99</v>
       </c>
     </row>
@@ -1911,92 +1910,92 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 59.5% slice</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>31206.94</v>
       </c>
-      <c r="D10" s="22" t="n">
-        <v>31206.94</v>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="D10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>Nairne's share of GP cut</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>262.24</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
+        <v>6244.65</v>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Raj Duggal — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="n">
         <v>262.24</v>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="D12" s="23" t="n">
+        <v>262.24</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Raj Duggal — direct 0.5%</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Phil — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>262.24</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>262.24</v>
       </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Direct member slice</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Phil — direct 0.5%</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>K-1</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>262.24</v>
-      </c>
-      <c r="D13" s="22" t="n">
-        <v>262.24</v>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
         </is>
@@ -2013,7 +2012,7 @@
         <v>31993.66</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>31993.66</v>
+        <v>6769.129999999999</v>
       </c>
       <c r="E14" s="7" t="n"/>
     </row>
@@ -2077,7 +2076,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2086,21 +2085,21 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>3218.29</v>
+        <v>1268.23</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3218.29</v>
+        <v>7500.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39% × his investors' perf fees</t>
+          <t>39% × her investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2109,14 +2108,14 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1268.23</v>
+        <v>3218.29</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1268.23</v>
+        <v>3218.29</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39% × her investors' perf fees</t>
+          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2153,7 @@
         <v>16589.52</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>16589.52</v>
+        <v>22821.89</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -2164,8 +2163,8 @@
           <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n">
-        <v>48583.18</v>
+      <c r="D24" s="17" t="n">
+        <v>29591.02</v>
       </c>
     </row>
     <row r="26">
@@ -2303,7 +2302,7 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>-48583.18</v>
+        <v>-29591.02</v>
       </c>
     </row>
     <row r="37">
@@ -2324,7 +2323,7 @@
       <c r="B38" s="34" t="n"/>
       <c r="C38" s="34" t="n"/>
       <c r="D38" s="35" t="n">
-        <v>-40176.19</v>
+        <v>-21184.03</v>
       </c>
       <c r="E38" s="34" t="n"/>
     </row>
@@ -2390,7 +2389,7 @@
           <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>57074.08999999997</v>
       </c>
     </row>
@@ -2429,92 +2428,92 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 59.5% slice</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>34183.9</v>
       </c>
-      <c r="D10" s="22" t="n">
-        <v>34183.9</v>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="D10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>Nairne's share of GP cut</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>287.26</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
+        <v>15531.01</v>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Raj Duggal — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="n">
         <v>287.26</v>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="D12" s="23" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Raj Duggal — direct 0.5%</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Phil — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>287.26</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>287.26</v>
       </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Direct member slice</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Phil — direct 0.5%</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>K-1</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>287.26</v>
-      </c>
-      <c r="D13" s="22" t="n">
-        <v>287.26</v>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
         </is>
@@ -2531,7 +2530,7 @@
         <v>35045.68000000001</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>35045.68000000001</v>
+        <v>16105.53</v>
       </c>
       <c r="E14" s="7" t="n"/>
     </row>
@@ -2572,7 +2571,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2581,21 +2580,21 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>15124.18</v>
+        <v>1833.52</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>15124.18</v>
+        <v>16567.16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>39% × his investors' perf fees</t>
+          <t>39% × her investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2604,10 +2603,10 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>4184.51</v>
+        <v>15124.18</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>4184.51</v>
+        <v>15124.18</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -2618,7 +2617,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2627,14 +2626,14 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1833.52</v>
+        <v>4184.51</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1833.52</v>
+        <v>4184.51</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39% × her investors' perf fees</t>
+          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2671,7 @@
         <v>21928.06</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>21928.06</v>
+        <v>36661.7</v>
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
@@ -2682,8 +2681,8 @@
           <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n">
-        <v>56973.74000000001</v>
+      <c r="D24" s="17" t="n">
+        <v>52767.23</v>
       </c>
     </row>
     <row r="26">
@@ -2805,7 +2804,7 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>-56973.74000000001</v>
+        <v>-52767.23</v>
       </c>
     </row>
     <row r="36">
@@ -2826,7 +2825,7 @@
       <c r="B37" s="34" t="n"/>
       <c r="C37" s="34" t="n"/>
       <c r="D37" s="35" t="n">
-        <v>-10249.65000000004</v>
+        <v>-6043.140000000029</v>
       </c>
       <c r="E37" s="34" t="n"/>
     </row>
@@ -2892,7 +2891,7 @@
           <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>16211.69</v>
       </c>
     </row>
@@ -2931,92 +2930,92 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 59.5% slice</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>9428.24</v>
       </c>
-      <c r="D10" s="22" t="n">
-        <v>9428.24</v>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="D10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>Nairne's share of GP cut</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>79.23</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
+        <v>4904.6</v>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>Direct member slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Raj Duggal — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="n">
         <v>79.23</v>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="D12" s="23" t="n">
+        <v>79.23</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Raj Duggal — direct 0.5%</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Phil — direct 0.5%</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>79.23</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>79.23</v>
       </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>Direct member slice</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Phil — direct 0.5%</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>K-1</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>79.23</v>
-      </c>
-      <c r="D13" s="22" t="n">
-        <v>79.23</v>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
         </is>
@@ -3033,7 +3032,7 @@
         <v>9665.929999999998</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>9665.929999999998</v>
+        <v>5063.059999999999</v>
       </c>
       <c r="E14" s="7" t="n"/>
     </row>
@@ -3074,7 +3073,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3083,21 +3082,21 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>4369.77</v>
+        <v>429.71</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>4369.77</v>
+        <v>5260.51</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>39% × his investors' perf fees</t>
+          <t>39% × her investors' perf fees</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3106,10 +3105,10 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>788.78</v>
+        <v>4369.77</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>788.78</v>
+        <v>4369.77</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -3120,7 +3119,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3129,14 +3128,14 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>429.71</v>
+        <v>788.78</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>429.71</v>
+        <v>788.78</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39% × her investors' perf fees</t>
+          <t>39% × his investors' perf fees</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3176,7 @@
       <c r="C22" s="6" t="n">
         <v>-278.48</v>
       </c>
-      <c r="D22" s="25" t="n">
+      <c r="D22" s="13" t="n">
         <v>-278.48</v>
       </c>
       <c r="E22" t="inlineStr">
@@ -3197,7 +3196,7 @@
         <v>5474.68</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>5474.68</v>
+        <v>10305.48</v>
       </c>
       <c r="E23" s="7" t="n"/>
     </row>
@@ -3207,8 +3206,8 @@
           <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="n">
-        <v>15140.61</v>
+      <c r="D25" s="17" t="n">
+        <v>15368.54</v>
       </c>
     </row>
     <row r="27">
@@ -3354,7 +3353,7 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>-15140.61</v>
+        <v>-15368.54</v>
       </c>
     </row>
     <row r="38">
@@ -3375,7 +3374,7 @@
       <c r="B39" s="34" t="n"/>
       <c r="C39" s="34" t="n"/>
       <c r="D39" s="35" t="n">
-        <v>-26028.92</v>
+        <v>-26256.85</v>
       </c>
       <c r="E39" s="34" t="n"/>
     </row>
@@ -3451,7 +3450,7 @@
       <c r="C4" s="6" t="n">
         <v>15140.61</v>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="13" t="n">
         <v>1071.080000000002</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -3593,11 +3592,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>10388.66</v>
+        <v>37139.89</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3615,11 +3614,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4152.7</v>
+        <v>10388.66</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3685,7 +3684,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>53544.62</v>
+        <v>86531.81</v>
       </c>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="11" t="n"/>
@@ -3696,14 +3695,14 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>K-1 partner cash distributions (NOT on 1099s): Nairne $85,996.83 + Raj $946.97 = $86,943.80</t>
+          <t>K-1 partner cash distributions (NOT on 1099s): Nairne $34,188.88 + Raj $946.97 = $35,135.85</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Cross-check: 1099 total ($53,544.62) + K-1 cash ($86,943.80) = $140,488.42; Gross perf fees per TPA = $153,023.03; delta = $12,534.61 (cash-vs-accrual timing + Aug TQ-T&amp;D excluded)</t>
+          <t>Cross-check: 1099 total ($86,531.81) + K-1 cash ($35,135.85) = $121,667.66; Gross perf fees per TPA = $153,023.03; delta = $31,355.37 (cash-vs-accrual timing + Aug TQ-T&amp;D excluded)</t>
         </is>
       </c>
     </row>
@@ -3786,10 +3785,10 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>85996.83</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>8118.108196721286</v>
+        <v>34188.88</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>-24328.30819672134</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -3807,8 +3806,8 @@
       <c r="C6" s="6" t="n">
         <v>946.97</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>67.65090163934406</v>
+      <c r="D6" s="13" t="n">
+        <v>-202.7359016393445</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
@@ -3826,8 +3825,8 @@
       <c r="C7" s="6" t="n">
         <v>946.97</v>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>67.65090163934406</v>
+      <c r="D7" s="13" t="n">
+        <v>-202.7359016393445</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
@@ -3849,7 +3848,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Less: 1099 contractor expenses (Alec/Jake/AJ/Issac/Luke): $53,544.62</t>
+          <t>Less: 1099 contractor expenses (Alec/Jake/AJ/Issac/Luke): $86,531.81</t>
         </is>
       </c>
     </row>
@@ -3862,76 +3861,76 @@
     </row>
     <row r="13">
       <c r="A13">
-        <f> Partnership NET INCOME (allocated to K-1s): $8,253.41</f>
+        <f> Partnership NET INCOME (allocated to K-1s): $-24,733.78</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nairne allocated share (98.36%): $8,118.11</t>
+          <t>Nairne allocated share (98.36%): $-24,328.31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Raj allocated share (0.82%): $67.65</t>
+          <t>Raj allocated share (0.82%): $-202.74</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phil allocated share (0.82%): $67.65</t>
+          <t>Phil allocated share (0.82%): $-202.74</t>
         </is>
       </c>
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Fund Mgmt 59.5% slice is Nairne's K-1 income (per Nairne 2026-04-30 — it's not a separate entity 1099).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Cash distributions and allocated K-1 net income are different things in partnership tax — Schedule K-1 reports both. The accountant will compute capital account changes.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Operating expenses include items that may be reclassed by the accountant (506c SPV Loans → balance sheet; Insurance $18k may need annual proration).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Cash-basis 1099s (above) may differ from accrual-basis (TPA-derived). Confirm GP's tax basis with accountant.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>TruQuant payments are excluded per Nairne 2026-04-30 (TQ is not a GP expense).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Ownership % shown (Nairne 98.36%/Raj 0.82%/Phil 0.82%) is derived from the 60/0.5/0.5 split. The actual LLC operating agreement governs — confirm with the accountant before filing.</t>
         </is>
@@ -4040,7 +4039,7 @@
           <t>Aug 2025</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="16" t="n">
         <v>18</v>
       </c>
       <c r="C4" s="6" t="n">
@@ -4071,7 +4070,7 @@
           <t>Sep 2025</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="16" t="n">
         <v>29</v>
       </c>
       <c r="C5" s="6" t="n">
@@ -4102,7 +4101,7 @@
           <t>Oct 2025</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="16" t="n">
         <v>35</v>
       </c>
       <c r="C6" s="6" t="n">
@@ -4133,7 +4132,7 @@
           <t>Nov 2025</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="16" t="n">
         <v>40</v>
       </c>
       <c r="C7" s="6" t="n">
@@ -4164,7 +4163,7 @@
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <v>45</v>
       </c>
       <c r="C8" s="6" t="n">
@@ -4317,7 +4316,7 @@
       <c r="F5" s="6" t="n">
         <v>4318.2789</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="17" t="n">
         <v>38691.4788</v>
       </c>
     </row>
@@ -4342,7 +4341,7 @@
       <c r="F6" s="6" t="n">
         <v>882.3828</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="17" t="n">
         <v>11298.2844</v>
       </c>
     </row>
@@ -4367,7 +4366,7 @@
       <c r="F7" s="6" t="n">
         <v>635.4503999999999</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="17" t="n">
         <v>4802.7564</v>
       </c>
     </row>
@@ -4392,7 +4391,7 @@
       <c r="F8" s="6" t="n">
         <v>374.5989</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="17" t="n">
         <v>3173.6757</v>
       </c>
     </row>
@@ -4417,7 +4416,7 @@
       <c r="F9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <v>1409.0037</v>
       </c>
     </row>
@@ -4442,7 +4441,7 @@
       <c r="F10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="17" t="n">
         <v>191.9346</v>
       </c>
     </row>
@@ -4467,7 +4466,7 @@
       <c r="F11" s="6" t="n">
         <v>74.38860000000001</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="17" t="n">
         <v>74.38860000000001</v>
       </c>
     </row>
@@ -4492,7 +4491,7 @@
       <c r="F12" s="6" t="n">
         <v>37.4595</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <v>37.4595</v>
       </c>
     </row>
@@ -4639,17 +4638,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Aug 2025 subtotal</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="18" t="n">
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="19" t="n">
         <v>10275</v>
       </c>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4657,7 +4656,7 @@
           <t>Sep 2025</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>(no GP-paid op expenses recorded)</t>
         </is>
@@ -4764,17 +4763,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Oct 2025 subtotal</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="18" t="n">
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="19" t="n">
         <v>43500</v>
       </c>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4852,17 +4851,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Nov 2025 subtotal</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="18" t="n">
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="19" t="n">
         <v>10350</v>
       </c>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4965,17 +4964,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Dec 2025 subtotal</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="18" t="n">
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="19" t="n">
         <v>27100</v>
       </c>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
     </row>
     <row r="23"/>
     <row r="24">
@@ -4993,42 +4992,42 @@
     </row>
     <row r="25"/>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Verify with user before sending to accountant</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>1. Insurance ($18k Dec): is this annual or already monthly-allocated? If annual, reduce to ~$1.5k for Dec.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>2. TPA fee duplication: Dec has TWO TPA lines ($600 + $4,500). The $600 also appears as fund-level admin in TPA's books. Confirm only the GP-paid portion goes here.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>3. 506c SPV Loan ($4,275 Aug + $25,000 Oct): is this an expense or a loan repayment? Expense for 1099/K-1 vs balance-sheet item.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>4. PVD ($6k Aug + $6k Oct): vendor identification needed for 1099 (if individual) or just expense (if entity).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>5. Badtwin / Ad Spend / Website (Oct): vendor names + 1099 obligations need confirmation.</t>
         </is>
@@ -5061,7 +5060,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -5120,184 +5119,184 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>Fund Mgmt 59.5% (= Nairne K-1)</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n">
-        <v>2815.16</v>
-      </c>
-      <c r="C5" s="22" t="n">
-        <v>7415.62</v>
-      </c>
-      <c r="D5" s="22" t="n">
-        <v>31206.94</v>
-      </c>
-      <c r="E5" s="22" t="n">
-        <v>34183.9</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>9428.24</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>85049.86</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>3172.12</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>3561.92</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>11848.88</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>15124.18</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>4369.77</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>38076.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3172.12</v>
+        <v>1743.04</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>3561.92</v>
+        <v>6068.58</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>11848.88</v>
+        <v>7500.6</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>15124.18</v>
+        <v>16567.16</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>4369.77</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>38076.87</v>
+        <v>5260.51</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>37139.89</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Jake Gordon</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>1266.18</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>930.9</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>3218.29</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>4184.51</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>788.78</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>10388.66</v>
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Nairne (K-1 partner)</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>1663.5</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>5845.12</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>6244.65</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>15531.01</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>4904.6</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>34188.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>335.47</v>
+        <v>1266.18</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>285.77</v>
+        <v>930.9</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1268.23</v>
+        <v>3218.29</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1833.52</v>
+        <v>4184.51</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>429.71</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>4152.7</v>
+        <v>788.78</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>10388.66</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Raj (K-1 partner)</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="23" t="n">
         <v>255.92</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <v>62.32</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>262.24</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="23" t="n">
         <v>287.26</v>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="23" t="n">
         <v>79.23</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="24" t="n">
         <v>946.97</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>Nairne (K-1 partner)</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Phil (K-1 partner)</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n">
         <v>255.92</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>62.32</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <v>262.24</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="23" t="n">
         <v>287.26</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="23" t="n">
         <v>79.23</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="24" t="n">
         <v>946.97</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>Phil (K-1 partner)</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="n">
-        <v>255.92</v>
-      </c>
-      <c r="C11" s="22" t="n">
-        <v>62.32</v>
-      </c>
-      <c r="D11" s="22" t="n">
-        <v>262.24</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>287.26</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>79.23</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>946.97</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Issac</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>254.12</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>785.85</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-278.48</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>761.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Issac</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
@@ -5307,41 +5306,41 @@
         <v>0</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>254.12</v>
+        <v>0</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>785.85</v>
+        <v>0</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>-278.48</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>761.49</v>
+        <v>164.9</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>164.9</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Luke</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Fund Mgmt 59.5% (= Nairne K-1)</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>164.9</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>164.9</v>
+      <c r="F13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5351,22 +5350,22 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>8356.690000000001</v>
+        <v>8356.68</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>12381.17</v>
+        <v>16531.16</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>48583.18</v>
+        <v>29591.02</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>56973.74000000001</v>
+        <v>52767.23</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>15140.61</v>
+        <v>15368.54</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>141435.39</v>
+        <v>122614.63</v>
       </c>
     </row>
     <row r="15">
@@ -5375,22 +5374,22 @@
           <t>TPA Perf Fees Crystallized (what was OWED)</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="25" t="n">
         <v>15355.51</v>
       </c>
-      <c r="C15" s="24" t="n">
+      <c r="C15" s="25" t="n">
         <v>12474.75</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="25" t="n">
         <v>51906.99</v>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="25" t="n">
         <v>57074.08999999997</v>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="F15" s="25" t="n">
         <v>16211.69</v>
       </c>
-      <c r="G15" s="24" t="n">
+      <c r="G15" s="25" t="n">
         <v>153023.03</v>
       </c>
     </row>
@@ -5400,23 +5399,23 @@
           <t>DELTA (Owed - Paid; positive = unpaid liability)</t>
         </is>
       </c>
-      <c r="B16" s="25" t="n">
-        <v>6998.820000000002</v>
-      </c>
-      <c r="C16" s="25" t="n">
-        <v>93.58000000000175</v>
-      </c>
-      <c r="D16" s="25" t="n">
-        <v>3323.809999999998</v>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>100.3499999999622</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>1071.080000000004</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>11587.63999999996</v>
+      <c r="B16" s="13" t="n">
+        <v>6998.830000000002</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>-4056.409999999998</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>22315.97</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>4306.859999999964</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>843.1500000000015</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>30408.39999999997</v>
       </c>
     </row>
   </sheetData>
@@ -5527,10 +5526,10 @@
       <c r="E5" s="6" t="n">
         <v>25000</v>
       </c>
-      <c r="H5" s="16" t="n">
+      <c r="H5" s="17" t="n">
         <v>29275</v>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>RECLASS: likely balance sheet item (loan/capital), not P&amp;L expense</t>
         </is>
@@ -5550,10 +5549,10 @@
       <c r="G6" s="6" t="n">
         <v>18000</v>
       </c>
-      <c r="H6" s="16" t="n">
+      <c r="H6" s="17" t="n">
         <v>18000</v>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>RECLASS: likely annual D&amp;O — pro-rate to ~$7,500 for Aug-Dec</t>
         </is>
@@ -5576,10 +5575,10 @@
       <c r="E7" s="6" t="n">
         <v>6000</v>
       </c>
-      <c r="H7" s="16" t="n">
+      <c r="H7" s="17" t="n">
         <v>12000</v>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>Vendor identification needed for 1099 obligation</t>
         </is>
@@ -5602,10 +5601,10 @@
       <c r="G8" s="6" t="n">
         <v>4000</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="17" t="n">
         <v>11500</v>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>Payroll/contractor — likely 1099 (already on consultant 1099 list?)</t>
         </is>
@@ -5625,10 +5624,10 @@
       <c r="E9" s="6" t="n">
         <v>7500</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="17" t="n">
         <v>7500</v>
       </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>Marketing/web build</t>
         </is>
@@ -5648,10 +5647,10 @@
       <c r="E10" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="H10" s="16" t="n">
+      <c r="H10" s="17" t="n">
         <v>5000</v>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>Marketing — vendor breakdown needed</t>
         </is>
@@ -5671,10 +5670,10 @@
       <c r="G11" s="6" t="n">
         <v>4500</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="17" t="n">
         <v>4500</v>
       </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>VERIFY: second TPA line in Dec — separate billing or duplicate?</t>
         </is>
@@ -5694,10 +5693,10 @@
       <c r="F12" s="6" t="n">
         <v>2250</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="17" t="n">
         <v>2250</v>
       </c>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>Compliance/verification service</t>
         </is>
@@ -5717,10 +5716,10 @@
       <c r="F13" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="I13" s="20" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>VERIFY: same as 'TPA (Formidium)' — TPA fee. Confirm GP-paid vs fund-paid.</t>
         </is>
@@ -5740,10 +5739,10 @@
       <c r="G14" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="I14" s="20" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>VERIFY: $600/mo also in fund-level admin (TPA books). May double-count.</t>
         </is>
@@ -5937,182 +5936,172 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 59.5% (Aug: 5.5%)</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
-        <v>2815.16</v>
-      </c>
+      <c r="C5" s="22" t="n"/>
       <c r="D5" s="29" t="n">
-        <v>2815.16</v>
-      </c>
-      <c r="E5" s="22" t="n">
-        <v>7415.62</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" s="22" t="n"/>
       <c r="F5" s="29" t="n">
-        <v>10230.78</v>
-      </c>
-      <c r="G5" s="22" t="n">
-        <v>31206.94</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5" s="22" t="n"/>
       <c r="H5" s="29" t="n">
-        <v>41437.72</v>
-      </c>
-      <c r="I5" s="22" t="n">
-        <v>34183.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="22" t="n"/>
       <c r="J5" s="29" t="n">
-        <v>75621.62</v>
-      </c>
-      <c r="K5" s="22" t="n">
-        <v>9428.24</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K5" s="22" t="n"/>
       <c r="L5" s="29" t="n">
-        <v>85049.86</v>
-      </c>
-      <c r="M5" s="23" t="n">
-        <v>85049.86</v>
+        <v>0</v>
+      </c>
+      <c r="M5" s="24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
-        <v>255.92</v>
+      <c r="C6" s="23" t="n">
+        <v>1663.5</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>255.92</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>62.32</v>
+        <v>1663.5</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>5845.12</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>318.24</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>262.24</v>
+        <v>7508.62</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>6244.65</v>
       </c>
       <c r="H6" s="29" t="n">
-        <v>580.48</v>
-      </c>
-      <c r="I6" s="22" t="n">
-        <v>287.26</v>
+        <v>13753.27</v>
+      </c>
+      <c r="I6" s="23" t="n">
+        <v>15531.01</v>
       </c>
       <c r="J6" s="29" t="n">
-        <v>867.74</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>79.23</v>
+        <v>29284.28</v>
+      </c>
+      <c r="K6" s="23" t="n">
+        <v>4904.6</v>
       </c>
       <c r="L6" s="29" t="n">
-        <v>946.97</v>
-      </c>
-      <c r="M6" s="23" t="n">
-        <v>946.97</v>
+        <v>34188.88</v>
+      </c>
+      <c r="M6" s="24" t="n">
+        <v>34188.88</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Raj Duggal — direct 0.5%</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>255.92</v>
       </c>
       <c r="D7" s="29" t="n">
         <v>255.92</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="23" t="n">
         <v>62.32</v>
       </c>
       <c r="F7" s="29" t="n">
         <v>318.24</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="23" t="n">
         <v>262.24</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>580.48</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="23" t="n">
         <v>287.26</v>
       </c>
       <c r="J7" s="29" t="n">
         <v>867.74</v>
       </c>
-      <c r="K7" s="22" t="n">
+      <c r="K7" s="23" t="n">
         <v>79.23</v>
       </c>
       <c r="L7" s="29" t="n">
         <v>946.97</v>
       </c>
-      <c r="M7" s="23" t="n">
+      <c r="M7" s="24" t="n">
         <v>946.97</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Phil — direct 0.5%</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>255.92</v>
       </c>
       <c r="D8" s="29" t="n">
         <v>255.92</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="23" t="n">
         <v>62.32</v>
       </c>
       <c r="F8" s="29" t="n">
         <v>318.24</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="23" t="n">
         <v>262.24</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>580.48</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="23" t="n">
         <v>287.26</v>
       </c>
       <c r="J8" s="29" t="n">
         <v>867.74</v>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="K8" s="23" t="n">
         <v>79.23</v>
       </c>
       <c r="L8" s="29" t="n">
         <v>946.97</v>
       </c>
-      <c r="M8" s="23" t="n">
+      <c r="M8" s="24" t="n">
         <v>946.97</v>
       </c>
     </row>
@@ -6157,14 +6146,14 @@
       <c r="L9" s="30" t="n">
         <v>38076.87</v>
       </c>
-      <c r="M9" s="16" t="n">
+      <c r="M9" s="17" t="n">
         <v>38076.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6173,43 +6162,43 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1266.18</v>
+        <v>1743.04</v>
       </c>
       <c r="D10" s="30" t="n">
-        <v>1266.18</v>
+        <v>1743.04</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>930.9</v>
+        <v>6068.58</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>2197.08</v>
+        <v>7811.62</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3218.29</v>
+        <v>7500.6</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>5415.37</v>
+        <v>15312.22</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>4184.51</v>
+        <v>16567.16</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>9599.880000000001</v>
+        <v>31879.38</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>788.78</v>
+        <v>5260.51</v>
       </c>
       <c r="L10" s="30" t="n">
-        <v>10388.66</v>
-      </c>
-      <c r="M10" s="16" t="n">
-        <v>10388.66</v>
+        <v>37139.89</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>37139.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6218,37 +6207,37 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>335.47</v>
+        <v>1266.18</v>
       </c>
       <c r="D11" s="30" t="n">
-        <v>335.47</v>
+        <v>1266.18</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>285.77</v>
+        <v>930.9</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>621.24</v>
+        <v>2197.08</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1268.23</v>
+        <v>3218.29</v>
       </c>
       <c r="H11" s="30" t="n">
-        <v>1889.47</v>
+        <v>5415.37</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1833.52</v>
+        <v>4184.51</v>
       </c>
       <c r="J11" s="30" t="n">
-        <v>3722.99</v>
+        <v>9599.880000000001</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>429.71</v>
+        <v>788.78</v>
       </c>
       <c r="L11" s="30" t="n">
-        <v>4152.7</v>
-      </c>
-      <c r="M11" s="16" t="n">
-        <v>4152.7</v>
+        <v>10388.66</v>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>10388.66</v>
       </c>
     </row>
     <row r="12">
@@ -6286,7 +6275,7 @@
       <c r="L12" s="30" t="n">
         <v>761.49</v>
       </c>
-      <c r="M12" s="16" t="n">
+      <c r="M12" s="17" t="n">
         <v>761.49</v>
       </c>
     </row>
@@ -6319,7 +6308,7 @@
       <c r="L13" s="30" t="n">
         <v>164.9</v>
       </c>
-      <c r="M13" s="16" t="n">
+      <c r="M13" s="17" t="n">
         <v>164.9</v>
       </c>
     </row>
@@ -6335,37 +6324,37 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>3582.92</v>
+        <v>2175.34</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>3582.92</v>
+        <v>2175.34</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>7602.579999999999</v>
+        <v>5969.759999999999</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>11185.5</v>
+        <v>8145.099999999999</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>31993.66</v>
+        <v>6769.129999999999</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>43179.16</v>
+        <v>14914.23</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>35045.68000000001</v>
+        <v>16105.53</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>78224.84000000001</v>
+        <v>31019.76</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>9665.929999999998</v>
+        <v>5063.059999999999</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>87890.77</v>
+        <v>36082.82</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>87890.77</v>
+        <v>36082.82</v>
       </c>
     </row>
     <row r="15">
@@ -6380,37 +6369,37 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>4773.77</v>
+        <v>6181.34</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>4773.77</v>
+        <v>6181.34</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>4778.59</v>
+        <v>10561.4</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>9552.360000000001</v>
+        <v>16742.74</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>16589.52</v>
+        <v>22821.89</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>26141.88</v>
+        <v>39564.63</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>21928.06</v>
+        <v>36661.7</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>48069.94</v>
+        <v>76226.32999999999</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>5474.68</v>
+        <v>10305.48</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>53544.62</v>
+        <v>86531.80999999998</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>53544.62</v>
+        <v>86531.80999999998</v>
       </c>
     </row>
     <row r="16">
@@ -6421,37 +6410,37 @@
       </c>
       <c r="B16" s="31" t="inlineStr"/>
       <c r="C16" s="32" t="n">
-        <v>8356.690000000001</v>
+        <v>8356.68</v>
       </c>
       <c r="D16" s="32" t="n">
-        <v>8356.690000000001</v>
+        <v>8356.68</v>
       </c>
       <c r="E16" s="32" t="n">
-        <v>12381.17</v>
+        <v>16531.16</v>
       </c>
       <c r="F16" s="32" t="n">
-        <v>20737.86</v>
+        <v>24887.84</v>
       </c>
       <c r="G16" s="32" t="n">
-        <v>48583.18</v>
+        <v>29591.02</v>
       </c>
       <c r="H16" s="32" t="n">
-        <v>69321.04000000001</v>
+        <v>54478.86</v>
       </c>
       <c r="I16" s="32" t="n">
-        <v>56973.74000000001</v>
+        <v>52767.23</v>
       </c>
       <c r="J16" s="32" t="n">
-        <v>126294.78</v>
+        <v>107246.09</v>
       </c>
       <c r="K16" s="32" t="n">
-        <v>15140.61</v>
+        <v>15368.54</v>
       </c>
       <c r="L16" s="32" t="n">
-        <v>141435.39</v>
+        <v>122614.63</v>
       </c>
       <c r="M16" s="32" t="n">
-        <v>141435.39</v>
+        <v>122614.63</v>
       </c>
     </row>
     <row r="17">
@@ -6461,27 +6450,27 @@
         </is>
       </c>
       <c r="B17" s="10" t="n"/>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="25" t="n">
         <v>15355.51</v>
       </c>
       <c r="D17" s="10" t="n"/>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="25" t="n">
         <v>12474.75</v>
       </c>
       <c r="F17" s="10" t="n"/>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="25" t="n">
         <v>51906.99</v>
       </c>
       <c r="H17" s="10" t="n"/>
-      <c r="I17" s="24" t="n">
+      <c r="I17" s="25" t="n">
         <v>57074.08999999997</v>
       </c>
       <c r="J17" s="10" t="n"/>
-      <c r="K17" s="24" t="n">
+      <c r="K17" s="25" t="n">
         <v>16211.69</v>
       </c>
       <c r="L17" s="10" t="n"/>
-      <c r="M17" s="24" t="n">
+      <c r="M17" s="25" t="n">
         <v>153023.03</v>
       </c>
     </row>
@@ -6492,66 +6481,66 @@
         </is>
       </c>
       <c r="B18" s="10" t="n"/>
-      <c r="C18" s="24" t="n">
+      <c r="C18" s="25" t="n">
         <v>10275</v>
       </c>
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="10" t="n"/>
       <c r="F18" s="10" t="n"/>
-      <c r="G18" s="24" t="n">
+      <c r="G18" s="25" t="n">
         <v>43500</v>
       </c>
       <c r="H18" s="10" t="n"/>
-      <c r="I18" s="24" t="n">
+      <c r="I18" s="25" t="n">
         <v>10350</v>
       </c>
       <c r="J18" s="10" t="n"/>
-      <c r="K18" s="24" t="n">
+      <c r="K18" s="25" t="n">
         <v>27100</v>
       </c>
       <c r="L18" s="10" t="n"/>
-      <c r="M18" s="24" t="n">
+      <c r="M18" s="25" t="n">
         <v>91225</v>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Payouts shown are NET — already after weighted costs (per Nairne 2026-04-30). The Distributions ledger's separate 'Gross vs Net' table tracks cumulative settlement balances (carries forward unpaid amounts) and a layer of Coinbase/wire/Crypto fees (~2.8%) plus per-person 'Expense' allocations (Nairne Expense, Alec Expense, etc.) — those are nested inside the Net amounts you see here.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>TruQuant payments are excluded entirely (per Nairne 2026-04-30). The Aug TruQuant amounts ($6,909.93 Trader &amp; Developer + $88.78 Spydr) and Sep Spydr $82.08 are NOT in any of the rows above.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Aug 2025 used a different waterfall (Fund Mgmt was 5.5% not 59.5%). From Sep onwards: standard 59.5% Mgmt + 39% Consultant + 0.5%×3 principals.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Issac shows -$278.48 in Dec — clawback against prior month overpayment.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Op Expenses row at the bottom is the GP-paid vendor expenses (not allocated to individuals on this tab — see Monthly Op Expenses tab for vendor breakdown).</t>
         </is>

--- a/2025-armada-prime-tech-1099-k1.xlsx
+++ b/2025-armada-prime-tech-1099-k1.xlsx
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>86531.81</v>
+        <v>86754.81</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>86531.81</v>
+        <v>86754.81</v>
       </c>
       <c r="C12" s="7" t="inlineStr"/>
     </row>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>-24733.78000000003</v>
+        <v>-24956.78000000003</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -859,15 +859,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Total cash out (1099s $86,531.81 + Nairne K-1 $34,188.88 + Raj K-1 $946.97 + Phil K-1 $946.97)</t>
+          <t>Total cash out (1099s $86,754.81 + Nairne K-1 $34,188.88 + Raj K-1 $946.97 + Phil K-1 $946.97)</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>122614.63</v>
+        <v>122837.63</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>vs Gross $153,023.03 — delta $30,408.40 (= retained / cash-vs-accrual / TQ exclusion)</t>
+          <t>vs Gross $153,023.03 — delta $30,185.40 (= retained / cash-vs-accrual / TQ exclusion)</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2661,173 +2661,192 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Nikki</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>223</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>1099 Subtotal</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="8" t="n">
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="8" t="n">
         <v>21928.06</v>
       </c>
-      <c r="D22" s="8" t="n">
-        <v>36661.7</v>
-      </c>
-      <c r="E22" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="D23" s="8" t="n">
+        <v>36884.7</v>
+      </c>
+      <c r="E23" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n">
-        <v>52767.23</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="33" t="inlineStr">
+      <c r="D25" s="17" t="n">
+        <v>52990.23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>OPERATING EXPENSES (paid by GP entity to vendors)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Chris</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Payroll/Contractor</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>7500</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alpha Verification</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Verification/Compliance</t>
+          <t>Payroll/Contractor</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>2250</v>
+        <v>7500</v>
       </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Alpha Verification</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Verification/Compliance</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Formidium (TPA)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Admin / TPA Fee</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C31" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>VERIFY GP-paid vs fund-paid</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Op Expenses Subtotal</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="8" t="n">
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="8" t="n">
         <v>10350</v>
       </c>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="33" t="inlineStr">
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t>RECONCILIATION</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Capital In (TPA Perf Fees Crystallized)</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>57074.08999999997</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Less: Cash to people (K-1 + 1099)</t>
+          <t>Capital In (TPA Perf Fees Crystallized)</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>-52767.23</v>
+        <v>57074.08999999997</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Less: Cash to people (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>-52990.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Less: Op expenses to vendors</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D37" s="6" t="n">
         <v>-10350</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7">
+    <row r="38">
+      <c r="A38" s="7">
         <f> Residual / (Deficit) for the month</f>
         <v/>
       </c>
-      <c r="B37" s="34" t="n"/>
-      <c r="C37" s="34" t="n"/>
-      <c r="D37" s="35" t="n">
-        <v>-6043.140000000029</v>
-      </c>
-      <c r="E37" s="34" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="34" t="n"/>
+      <c r="D38" s="35" t="n">
+        <v>-6266.140000000029</v>
+      </c>
+      <c r="E38" s="34" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3509,7 +3528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3658,11 +3677,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>164.9</v>
+        <v>223</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3678,31 +3697,53 @@
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>164.9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Individual 1099</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>From Distributions ledger (cash actually paid)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>TOTAL 1099 PAYMENTS</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
-        <v>86531.81</v>
-      </c>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>K-1 partner cash distributions (NOT on 1099s): Nairne $34,188.88 + Raj $946.97 = $35,135.85</t>
-        </is>
-      </c>
-    </row>
+      <c r="B11" s="12" t="n">
+        <v>86754.81</v>
+      </c>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Cross-check: 1099 total ($86,531.81) + K-1 cash ($35,135.85) = $121,667.66; Gross perf fees per TPA = $153,023.03; delta = $31,355.37 (cash-vs-accrual timing + Aug TQ-T&amp;D excluded)</t>
+          <t>K-1 partner cash distributions (NOT on 1099s): Nairne $34,188.88 + Raj $946.97 = $35,135.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Cross-check: 1099 total ($86,754.81) + K-1 cash ($35,135.85) = $121,890.66; Gross perf fees per TPA = $153,023.03; delta = $31,132.37 (cash-vs-accrual timing + Aug TQ-T&amp;D excluded)</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3829,7 @@
         <v>34188.88</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>-24328.30819672134</v>
+        <v>-24547.65245901642</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -3807,7 +3848,7 @@
         <v>946.97</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>-202.7359016393445</v>
+        <v>-204.5637704918035</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
@@ -3826,7 +3867,7 @@
         <v>946.97</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>-202.7359016393445</v>
+        <v>-204.5637704918035</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
@@ -3848,7 +3889,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Less: 1099 contractor expenses (Alec/Jake/AJ/Issac/Luke): $86,531.81</t>
+          <t>Less: 1099 contractor expenses (Alec/Jake/AJ/Issac/Luke): $86,754.81</t>
         </is>
       </c>
     </row>
@@ -3861,28 +3902,28 @@
     </row>
     <row r="13">
       <c r="A13">
-        <f> Partnership NET INCOME (allocated to K-1s): $-24,733.78</f>
+        <f> Partnership NET INCOME (allocated to K-1s): $-24,956.78</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nairne allocated share (98.36%): $-24,328.31</t>
+          <t>Nairne allocated share (98.36%): $-24,547.65</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Raj allocated share (0.82%): $-202.74</t>
+          <t>Raj allocated share (0.82%): $-204.56</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phil allocated share (0.82%): $-202.74</t>
+          <t>Phil allocated share (0.82%): $-204.56</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5296,7 +5337,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
@@ -5309,113 +5350,138 @@
         <v>0</v>
       </c>
       <c r="E12" s="6" t="n">
+        <v>223</v>
+      </c>
+      <c r="F12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="17" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
         <v>164.9</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G13" s="17" t="n">
         <v>164.9</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Fund Mgmt 59.5% (= Nairne K-1)</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B14" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C14" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D14" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E14" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F14" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G14" s="24" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>MONTH TOTAL (cash actually paid out)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B15" s="12" t="n">
         <v>8356.68</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C15" s="12" t="n">
         <v>16531.16</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D15" s="12" t="n">
         <v>29591.02</v>
       </c>
-      <c r="E14" s="12" t="n">
-        <v>52767.23</v>
-      </c>
-      <c r="F14" s="12" t="n">
+      <c r="E15" s="12" t="n">
+        <v>52990.23</v>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>15368.54</v>
       </c>
-      <c r="G14" s="12" t="n">
-        <v>122614.63</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="G15" s="12" t="n">
+        <v>122837.63</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>TPA Perf Fees Crystallized (what was OWED)</t>
         </is>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B16" s="25" t="n">
         <v>15355.51</v>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C16" s="25" t="n">
         <v>12474.75</v>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D16" s="25" t="n">
         <v>51906.99</v>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E16" s="25" t="n">
         <v>57074.08999999997</v>
       </c>
-      <c r="F15" s="25" t="n">
+      <c r="F16" s="25" t="n">
         <v>16211.69</v>
       </c>
-      <c r="G15" s="25" t="n">
+      <c r="G16" s="25" t="n">
         <v>153023.03</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>DELTA (Owed - Paid; positive = unpaid liability)</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B17" s="13" t="n">
         <v>6998.830000000002</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C17" s="13" t="n">
         <v>-4056.409999999998</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D17" s="13" t="n">
         <v>22315.97</v>
       </c>
-      <c r="E16" s="13" t="n">
-        <v>4306.859999999964</v>
-      </c>
-      <c r="F16" s="13" t="n">
+      <c r="E17" s="13" t="n">
+        <v>4083.859999999964</v>
+      </c>
+      <c r="F17" s="13" t="n">
         <v>843.1500000000015</v>
       </c>
-      <c r="G16" s="13" t="n">
-        <v>30408.39999999997</v>
+      <c r="G17" s="13" t="n">
+        <v>30185.39999999997</v>
       </c>
     </row>
   </sheetData>
@@ -5835,7 +5901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -6282,7 +6348,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Nikki</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6299,248 +6365,281 @@
       <c r="H13" s="30" t="n">
         <v>0</v>
       </c>
+      <c r="I13" s="6" t="n">
+        <v>223</v>
+      </c>
       <c r="J13" s="30" t="n">
+        <v>223</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>223</v>
+      </c>
+      <c r="M13" s="17" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="F14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="n">
         <v>164.9</v>
       </c>
-      <c r="L13" s="30" t="n">
+      <c r="L14" s="30" t="n">
         <v>164.9</v>
       </c>
-      <c r="M13" s="17" t="n">
+      <c r="M14" s="17" t="n">
         <v>164.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>K-1 SUBTOTAL (Nairne + Raj + Phil)</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>K-1</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>2175.34</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>2175.34</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>5969.759999999999</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>8145.099999999999</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>6769.129999999999</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>14914.23</v>
-      </c>
-      <c r="I14" s="12" t="n">
-        <v>16105.53</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>31019.76</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>5063.059999999999</v>
-      </c>
-      <c r="L14" s="12" t="n">
-        <v>36082.82</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>36082.82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
+          <t>K-1 SUBTOTAL (Nairne + Raj + Phil)</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>K-1</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>2175.34</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>2175.34</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>5969.759999999999</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>8145.099999999999</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>6769.129999999999</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>14914.23</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>16105.53</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>31019.76</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>5063.059999999999</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>36082.82</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>36082.82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
           <t>1099 SUBTOTAL (consultants only)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>1099</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C16" s="12" t="n">
         <v>6181.34</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D16" s="12" t="n">
         <v>6181.34</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>10561.4</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>16742.74</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>22821.89</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>39564.63</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>36661.7</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>76226.32999999999</v>
-      </c>
-      <c r="K15" s="12" t="n">
+      <c r="I16" s="12" t="n">
+        <v>36884.7</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>76449.32999999999</v>
+      </c>
+      <c r="K16" s="12" t="n">
         <v>10305.48</v>
       </c>
-      <c r="L15" s="12" t="n">
-        <v>86531.80999999998</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>86531.80999999998</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="L16" s="12" t="n">
+        <v>86754.80999999998</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>86754.80999999998</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>GRAND TOTAL (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="B16" s="31" t="inlineStr"/>
-      <c r="C16" s="32" t="n">
+      <c r="B17" s="31" t="inlineStr"/>
+      <c r="C17" s="32" t="n">
         <v>8356.68</v>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D17" s="32" t="n">
         <v>8356.68</v>
       </c>
-      <c r="E16" s="32" t="n">
+      <c r="E17" s="32" t="n">
         <v>16531.16</v>
       </c>
-      <c r="F16" s="32" t="n">
+      <c r="F17" s="32" t="n">
         <v>24887.84</v>
       </c>
-      <c r="G16" s="32" t="n">
+      <c r="G17" s="32" t="n">
         <v>29591.02</v>
       </c>
-      <c r="H16" s="32" t="n">
+      <c r="H17" s="32" t="n">
         <v>54478.86</v>
       </c>
-      <c r="I16" s="32" t="n">
-        <v>52767.23</v>
-      </c>
-      <c r="J16" s="32" t="n">
-        <v>107246.09</v>
-      </c>
-      <c r="K16" s="32" t="n">
+      <c r="I17" s="32" t="n">
+        <v>52990.23</v>
+      </c>
+      <c r="J17" s="32" t="n">
+        <v>107469.09</v>
+      </c>
+      <c r="K17" s="32" t="n">
         <v>15368.54</v>
       </c>
-      <c r="L16" s="32" t="n">
-        <v>122614.63</v>
-      </c>
-      <c r="M16" s="32" t="n">
-        <v>122614.63</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>TPA Perf Fees Crystallized (Gross GP Income)</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="25" t="n">
-        <v>15355.51</v>
-      </c>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="25" t="n">
-        <v>12474.75</v>
-      </c>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="25" t="n">
-        <v>51906.99</v>
-      </c>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="25" t="n">
-        <v>57074.08999999997</v>
-      </c>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="25" t="n">
-        <v>16211.69</v>
-      </c>
-      <c r="L17" s="10" t="n"/>
-      <c r="M17" s="25" t="n">
-        <v>153023.03</v>
+      <c r="L17" s="32" t="n">
+        <v>122837.63</v>
+      </c>
+      <c r="M17" s="32" t="n">
+        <v>122837.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Op Expenses (paid from GP retained)</t>
+          <t>TPA Perf Fees Crystallized (Gross GP Income)</t>
         </is>
       </c>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="25" t="n">
-        <v>10275</v>
+        <v>15355.51</v>
       </c>
       <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
+      <c r="E18" s="25" t="n">
+        <v>12474.75</v>
+      </c>
       <c r="F18" s="10" t="n"/>
       <c r="G18" s="25" t="n">
-        <v>43500</v>
+        <v>51906.99</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="25" t="n">
-        <v>10350</v>
+        <v>57074.08999999997</v>
       </c>
       <c r="J18" s="10" t="n"/>
       <c r="K18" s="25" t="n">
-        <v>27100</v>
+        <v>16211.69</v>
       </c>
       <c r="L18" s="10" t="n"/>
       <c r="M18" s="25" t="n">
+        <v>153023.03</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Op Expenses (paid from GP retained)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="25" t="n">
+        <v>10275</v>
+      </c>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="25" t="n">
+        <v>43500</v>
+      </c>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="25" t="n">
+        <v>10350</v>
+      </c>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="25" t="n">
+        <v>27100</v>
+      </c>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="25" t="n">
         <v>91225</v>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="35" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Payouts shown are NET — already after weighted costs (per Nairne 2026-04-30). The Distributions ledger's separate 'Gross vs Net' table tracks cumulative settlement balances (carries forward unpaid amounts) and a layer of Coinbase/wire/Crypto fees (~2.8%) plus per-person 'Expense' allocations (Nairne Expense, Alec Expense, etc.) — those are nested inside the Net amounts you see here.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>TruQuant payments are excluded entirely (per Nairne 2026-04-30). The Aug TruQuant amounts ($6,909.93 Trader &amp; Developer + $88.78 Spydr) and Sep Spydr $82.08 are NOT in any of the rows above.</t>
+          <t>Payouts shown are NET — already after weighted costs (per Nairne 2026-04-30). The Distributions ledger's separate 'Gross vs Net' table tracks cumulative settlement balances (carries forward unpaid amounts) and a layer of Coinbase/wire/Crypto fees (~2.8%) plus per-person 'Expense' allocations (Nairne Expense, Alec Expense, etc.) — those are nested inside the Net amounts you see here.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Aug 2025 used a different waterfall (Fund Mgmt was 5.5% not 59.5%). From Sep onwards: standard 59.5% Mgmt + 39% Consultant + 0.5%×3 principals.</t>
+          <t>TruQuant payments are excluded entirely (per Nairne 2026-04-30). The Aug TruQuant amounts ($6,909.93 Trader &amp; Developer + $88.78 Spydr) and Sep Spydr $82.08 are NOT in any of the rows above.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Issac shows -$278.48 in Dec — clawback against prior month overpayment.</t>
+          <t>Aug 2025 used a different waterfall (Fund Mgmt was 5.5% not 59.5%). From Sep onwards: standard 59.5% Mgmt + 39% Consultant + 0.5%×3 principals.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Issac shows -$278.48 in Dec — clawback against prior month overpayment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="35" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Op Expenses row at the bottom is the GP-paid vendor expenses (not allocated to individuals on this tab — see Monthly Op Expenses tab for vendor breakdown).</t>
         </is>
@@ -6551,7 +6650,7 @@
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A23:M23"/>
     <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A26:M26"/>
     <mergeCell ref="A25:M25"/>
     <mergeCell ref="A24:M24"/>
     <mergeCell ref="A2:M2"/>

--- a/2025-armada-prime-tech-1099-k1.xlsx
+++ b/2025-armada-prime-tech-1099-k1.xlsx
@@ -159,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,7 +175,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -192,6 +191,7 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,6 +202,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -718,7 +719,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>91225</v>
+        <v>55225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -737,7 +738,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>-24956.78000000003</v>
+        <v>11043.21999999997</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -943,7 +944,7 @@
           <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="16" t="n">
         <v>15355.51</v>
       </c>
     </row>
@@ -982,92 +983,92 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 5.5% slice</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="22" t="n">
         <v>2815.16</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>Nairne's share of GP cut</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="22" t="n">
         <v>255.92</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="22" t="n">
         <v>1663.5</v>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Raj Duggal — direct 0.5%</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="22" t="n">
         <v>255.92</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="22" t="n">
         <v>255.92</v>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Phil — direct 0.5%</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="22" t="n">
         <v>255.92</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="22" t="n">
         <v>255.92</v>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
         </is>
@@ -1212,7 +1213,7 @@
           <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="16" t="n">
         <v>8356.68</v>
       </c>
     </row>
@@ -1274,7 +1275,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PVD (verify)</t>
+          <t>Tech/Ads</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
@@ -1345,28 +1346,28 @@
       <c r="E35" s="34" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>AUG NOTES:</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>TruQuant payments excluded: $6,909.93 'Trader &amp; Developer' (13.5%) + $88.78 Spydr — total $6,998.71. These are upstream of the GP entity per Nairne 2026-04-30.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>If you ADD BACK the $6,998.71 TQ-excluded amounts, total cash flow ties to the full $15,355.51 GP cut: $8,356.69 (people) + $6,998.71 (TQ) = $15,355.40.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>Op expenses ($10,275 SPV+PVD) are funded out of GP retained earnings, NOT from people's slices.</t>
         </is>
@@ -1437,7 +1438,7 @@
           <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="16" t="n">
         <v>12474.75</v>
       </c>
     </row>
@@ -1476,92 +1477,92 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 59.5% slice</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="22" t="n">
         <v>7415.62</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>Nairne's share of GP cut</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="22" t="n">
         <v>62.32</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="22" t="n">
         <v>5845.12</v>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Raj Duggal — direct 0.5%</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="22" t="n">
         <v>62.32</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="22" t="n">
         <v>62.32</v>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Phil — direct 0.5%</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="22" t="n">
         <v>62.32</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="22" t="n">
         <v>62.32</v>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
         </is>
@@ -1706,7 +1707,7 @@
           <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="16" t="n">
         <v>16531.16</v>
       </c>
     </row>
@@ -1741,7 +1742,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>(no GP-paid op expenses recorded for this month)</t>
         </is>
@@ -1824,7 +1825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1871,7 +1872,7 @@
           <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="16" t="n">
         <v>51906.99</v>
       </c>
     </row>
@@ -1910,92 +1911,92 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 59.5% slice</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="22" t="n">
         <v>31206.94</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>Nairne's share of GP cut</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="22" t="n">
         <v>262.24</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="22" t="n">
         <v>6244.65</v>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Raj Duggal — direct 0.5%</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="22" t="n">
         <v>262.24</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="22" t="n">
         <v>262.24</v>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Phil — direct 0.5%</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="22" t="n">
         <v>262.24</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="22" t="n">
         <v>262.24</v>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
         </is>
@@ -2163,7 +2164,7 @@
           <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="16" t="n">
         <v>29591.02</v>
       </c>
     </row>
@@ -2200,132 +2201,80 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>506c SPV Loan</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Loan/SPV</t>
+          <t>Marketing/Web</t>
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RECLASS: likely balance sheet, not P&amp;L</t>
-        </is>
-      </c>
+        <v>7500</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>PVD (verify)</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Marketing/Web</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="n">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Op Expenses Subtotal</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="8" t="n">
         <v>7500</v>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Ad Spend</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Marketing/Ads</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>RECONCILIATION</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Op Expenses Subtotal</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="8" t="n">
-        <v>43500</v>
-      </c>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Capital In (TPA Perf Fees Crystallized)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>51906.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Less: Cash to people (K-1 + 1099)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-29591.02</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="33" t="inlineStr">
-        <is>
-          <t>RECONCILIATION</t>
-        </is>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Less: Op expenses to vendors</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>-7500</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Capital In (TPA Perf Fees Crystallized)</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>51906.99</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Less: Cash to people (K-1 + 1099)</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="n">
-        <v>-29591.02</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Less: Op expenses to vendors</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>-43500</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7">
+      <c r="A35" s="7">
         <f> Residual / (Deficit) for the month</f>
         <v/>
       </c>
-      <c r="B38" s="34" t="n"/>
-      <c r="C38" s="34" t="n"/>
-      <c r="D38" s="35" t="n">
-        <v>-21184.03</v>
-      </c>
-      <c r="E38" s="34" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="34" t="n"/>
+      <c r="D35" s="36" t="n">
+        <v>14815.97</v>
+      </c>
+      <c r="E35" s="34" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2389,7 +2338,7 @@
           <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="16" t="n">
         <v>57074.08999999997</v>
       </c>
     </row>
@@ -2428,92 +2377,92 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 59.5% slice</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="22" t="n">
         <v>34183.9</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>Nairne's share of GP cut</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="22" t="n">
         <v>287.26</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="22" t="n">
         <v>15531.01</v>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Raj Duggal — direct 0.5%</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="22" t="n">
         <v>287.26</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="22" t="n">
         <v>287.26</v>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Phil — direct 0.5%</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="22" t="n">
         <v>287.26</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="22" t="n">
         <v>287.26</v>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
         </is>
@@ -2700,7 +2649,7 @@
           <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="16" t="n">
         <v>52990.23</v>
       </c>
     </row>
@@ -2737,12 +2686,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Payroll/Contractor</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="C29" s="6" t="n">
@@ -2910,7 +2859,7 @@
           <t xml:space="preserve">  GP Cut: Performance Fees Crystallized (TPA — 30% of fund net)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="16" t="n">
         <v>16211.69</v>
       </c>
     </row>
@@ -2949,92 +2898,92 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 59.5% slice</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="22" t="n">
         <v>9428.24</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>Nairne's share of GP cut</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="22" t="n">
         <v>79.23</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="22" t="n">
         <v>4904.6</v>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Raj Duggal — direct 0.5%</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="22" t="n">
         <v>79.23</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="22" t="n">
         <v>79.23</v>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>Direct member slice</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Phil — direct 0.5%</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="22" t="n">
         <v>79.23</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="22" t="n">
         <v>79.23</v>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>Direct member slice (Phil is K-1 per Nairne 2026-05-05)</t>
         </is>
@@ -3195,7 +3144,7 @@
       <c r="C22" s="6" t="n">
         <v>-278.48</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="25" t="n">
         <v>-278.48</v>
       </c>
       <c r="E22" t="inlineStr">
@@ -3225,7 +3174,7 @@
           <t>TOTAL CASH PAID TO PEOPLE (K-1 + 1099)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="16" t="n">
         <v>15368.54</v>
       </c>
     </row>
@@ -3469,7 +3418,7 @@
       <c r="C4" s="6" t="n">
         <v>15140.61</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="25" t="n">
         <v>1071.080000000002</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -3828,8 +3777,8 @@
       <c r="C5" s="6" t="n">
         <v>34188.88</v>
       </c>
-      <c r="D5" s="13" t="n">
-        <v>-24547.65245901642</v>
+      <c r="D5" s="6" t="n">
+        <v>10862.18360655735</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -3847,8 +3796,8 @@
       <c r="C6" s="6" t="n">
         <v>946.97</v>
       </c>
-      <c r="D6" s="13" t="n">
-        <v>-204.5637704918035</v>
+      <c r="D6" s="6" t="n">
+        <v>90.51819672131126</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
@@ -3866,8 +3815,8 @@
       <c r="C7" s="6" t="n">
         <v>946.97</v>
       </c>
-      <c r="D7" s="13" t="n">
-        <v>-204.5637704918035</v>
+      <c r="D7" s="6" t="n">
+        <v>90.51819672131126</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
@@ -3896,82 +3845,82 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Less: GP-paid operating expenses: $91,225.00</t>
+          <t>Less: GP-paid operating expenses: $55,225.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <f> Partnership NET INCOME (allocated to K-1s): $-24,956.78</f>
+        <f> Partnership NET INCOME (allocated to K-1s): $11,043.22</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nairne allocated share (98.36%): $-24,547.65</t>
+          <t>Nairne allocated share (98.36%): $10,862.18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Raj allocated share (0.82%): $-204.56</t>
+          <t>Raj allocated share (0.82%): $90.52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phil allocated share (0.82%): $-204.56</t>
+          <t>Phil allocated share (0.82%): $90.52</t>
         </is>
       </c>
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Fund Mgmt 59.5% slice is Nairne's K-1 income (per Nairne 2026-04-30 — it's not a separate entity 1099).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Cash distributions and allocated K-1 net income are different things in partnership tax — Schedule K-1 reports both. The accountant will compute capital account changes.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Operating expenses include items that may be reclassed by the accountant (506c SPV Loans → balance sheet; Insurance $18k may need annual proration).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Cash-basis 1099s (above) may differ from accrual-basis (TPA-derived). Confirm GP's tax basis with accountant.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>TruQuant payments are excluded per Nairne 2026-04-30 (TQ is not a GP expense).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Ownership % shown (Nairne 98.36%/Raj 0.82%/Phil 0.82%) is derived from the 60/0.5/0.5 split. The actual LLC operating agreement governs — confirm with the accountant before filing.</t>
         </is>
@@ -4080,7 +4029,7 @@
           <t>Aug 2025</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="15" t="n">
         <v>18</v>
       </c>
       <c r="C4" s="6" t="n">
@@ -4111,7 +4060,7 @@
           <t>Sep 2025</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="15" t="n">
         <v>29</v>
       </c>
       <c r="C5" s="6" t="n">
@@ -4142,7 +4091,7 @@
           <t>Oct 2025</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="15" t="n">
         <v>35</v>
       </c>
       <c r="C6" s="6" t="n">
@@ -4173,7 +4122,7 @@
           <t>Nov 2025</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>40</v>
       </c>
       <c r="C7" s="6" t="n">
@@ -4204,7 +4153,7 @@
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>45</v>
       </c>
       <c r="C8" s="6" t="n">
@@ -4357,7 +4306,7 @@
       <c r="F5" s="6" t="n">
         <v>4318.2789</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="16" t="n">
         <v>38691.4788</v>
       </c>
     </row>
@@ -4382,7 +4331,7 @@
       <c r="F6" s="6" t="n">
         <v>882.3828</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="16" t="n">
         <v>11298.2844</v>
       </c>
     </row>
@@ -4407,7 +4356,7 @@
       <c r="F7" s="6" t="n">
         <v>635.4503999999999</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="16" t="n">
         <v>4802.7564</v>
       </c>
     </row>
@@ -4432,7 +4381,7 @@
       <c r="F8" s="6" t="n">
         <v>374.5989</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>3173.6757</v>
       </c>
     </row>
@@ -4457,7 +4406,7 @@
       <c r="F9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="16" t="n">
         <v>1409.0037</v>
       </c>
     </row>
@@ -4482,7 +4431,7 @@
       <c r="F10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="16" t="n">
         <v>191.9346</v>
       </c>
     </row>
@@ -4507,7 +4456,7 @@
       <c r="F11" s="6" t="n">
         <v>74.38860000000001</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="16" t="n">
         <v>74.38860000000001</v>
       </c>
     </row>
@@ -4532,7 +4481,7 @@
       <c r="F12" s="6" t="n">
         <v>37.4595</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="16" t="n">
         <v>37.4595</v>
       </c>
     </row>
@@ -4576,7 +4525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4669,7 +4618,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PVD (verify)</t>
+          <t>Tech/Ads</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4679,17 +4628,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Aug 2025 subtotal</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="19" t="n">
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="18" t="n">
         <v>10275</v>
       </c>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4697,7 +4646,7 @@
           <t>Sep 2025</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>(no GP-paid op expenses recorded)</t>
         </is>
@@ -4711,15 +4660,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>506c SPV Loan</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Loan/SPV</t>
+          <t>Marketing/Web</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4729,39 +4678,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Oct 2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PVD</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PVD (verify)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Distributions ledger — Oct 2025 sheet</t>
-        </is>
-      </c>
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Oct 2025 subtotal</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Oct 2025</t>
+          <t>Nov 2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
@@ -4769,112 +4706,112 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Marketing/Web</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Distributions ledger — Oct 2025 sheet</t>
+          <t>Distributions ledger — Nov 2025 sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oct 2025</t>
+          <t>Nov 2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ad Spend</t>
+          <t>Alpha Verification</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>5000</v>
+        <v>2250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Marketing/Ads</t>
+          <t>Verification/Compliance</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Distributions ledger — Oct 2025 sheet</t>
+          <t>Distributions ledger — Nov 2025 sheet</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>Oct 2025 subtotal</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="n"/>
-      <c r="C13" s="19" t="n">
-        <v>43500</v>
-      </c>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Formidium (TPA)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Admin / TPA Fee</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Distributions ledger — Nov 2025 sheet</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Nov 2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Chris</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Payroll/Contractor</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Distributions ledger — Nov 2025 sheet</t>
-        </is>
-      </c>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Nov 2025 subtotal</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="18" t="n">
+        <v>10350</v>
+      </c>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nov 2025</t>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alpha Verification</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>2250</v>
+        <v>4000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Verification/Compliance</t>
+          <t>Payroll/Contractor</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Distributions ledger — Nov 2025 sheet</t>
+          <t>BEST ONE Dec Costs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nov 2025</t>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Formidium (TPA)</t>
+          <t>TPA (Formidium)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
@@ -4887,22 +4824,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Distributions ledger — Nov 2025 sheet</t>
+          <t>BEST ONE Dec Costs</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Nov 2025 subtotal</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="19" t="n">
-        <v>10350</v>
-      </c>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BEST ONE Dec Costs</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4912,15 +4861,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>TPA (second line)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Payroll/Contractor</t>
+          <t>Admin / TPA Fee</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4930,158 +4879,83 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Dec 2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TPA (Formidium)</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>600</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Admin / TPA Fee</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>BEST ONE Dec Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Dec 2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>18000</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>BEST ONE Dec Costs</t>
-        </is>
-      </c>
-    </row>
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Dec 2025 subtotal</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="18" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Dec 2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>TPA (second line)</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>4500</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Admin / TPA Fee</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>BEST ONE Dec Costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Dec 2025 subtotal</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="19" t="n">
-        <v>27100</v>
-      </c>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-    </row>
-    <row r="23"/>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>2025 TOTAL GP-PAID OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="12" t="n">
+        <v>55225</v>
+      </c>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Verify with user before sending to accountant</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>2025 TOTAL GP-PAID OPERATING EXPENSES</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="12" t="n">
-        <v>91225</v>
-      </c>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-    </row>
-    <row r="25"/>
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>1. Insurance ($18k Dec): is this annual or already monthly-allocated? If annual D&amp;O policy, fully deductible in 2025 under 12-month prepaid rule (Reg §1.263(a)-4(f)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>2. TPA fee duplication: Dec has TWO TPA lines ($600 + $4,500). The $600 also appears as fund-level admin in TPA's books. Confirm only the GP-paid portion goes here.</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Verify with user before sending to accountant</t>
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>3. 506c SPV Loan ($4,275 Aug only): is this an expense or a loan repayment? If loan, reclassify to Balance Sheet (asset).</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>1. Insurance ($18k Dec): is this annual or already monthly-allocated? If annual, reduce to ~$1.5k for Dec.</t>
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>4. PVD ($6k Aug only): vendor identification needed for 1099 (if individual) or just expense (if entity). Tech/Ads category.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>2. TPA fee duplication: Dec has TWO TPA lines ($600 + $4,500). The $600 also appears as fund-level admin in TPA's books. Confirm only the GP-paid portion goes here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>3. 506c SPV Loan ($4,275 Aug + $25,000 Oct): is this an expense or a loan repayment? Expense for 1099/K-1 vs balance-sheet item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>4. PVD ($6k Aug + $6k Oct): vendor identification needed for 1099 (if individual) or just expense (if entity).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr">
-        <is>
-          <t>5. Badtwin / Ad Spend / Website (Oct): vendor names + 1099 obligations need confirmation.</t>
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>5. Consulting ($7.5k Nov) + Chris ($4k Dec): 1099-NEC required if individuals.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A31:E31"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5180,7 +5054,7 @@
       <c r="F5" s="6" t="n">
         <v>4369.77</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="16" t="n">
         <v>38076.87</v>
       </c>
     </row>
@@ -5205,32 +5079,32 @@
       <c r="F6" s="6" t="n">
         <v>5260.51</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="16" t="n">
         <v>37139.89</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Nairne (K-1 partner)</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="22" t="n">
         <v>1663.5</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="22" t="n">
         <v>5845.12</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="22" t="n">
         <v>6244.65</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="22" t="n">
         <v>15531.01</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="22" t="n">
         <v>4904.6</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="23" t="n">
         <v>34188.88</v>
       </c>
     </row>
@@ -5255,57 +5129,57 @@
       <c r="F8" s="6" t="n">
         <v>788.78</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="16" t="n">
         <v>10388.66</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Raj (K-1 partner)</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="22" t="n">
         <v>255.92</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="22" t="n">
         <v>62.32</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="22" t="n">
         <v>262.24</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="22" t="n">
         <v>287.26</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="22" t="n">
         <v>79.23</v>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="23" t="n">
         <v>946.97</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Phil (K-1 partner)</t>
         </is>
       </c>
-      <c r="B10" s="23" t="n">
+      <c r="B10" s="22" t="n">
         <v>255.92</v>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C10" s="22" t="n">
         <v>62.32</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="22" t="n">
         <v>262.24</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="22" t="n">
         <v>287.26</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="22" t="n">
         <v>79.23</v>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="23" t="n">
         <v>946.97</v>
       </c>
     </row>
@@ -5330,7 +5204,7 @@
       <c r="F11" s="6" t="n">
         <v>-278.48</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="16" t="n">
         <v>761.49</v>
       </c>
     </row>
@@ -5355,7 +5229,7 @@
       <c r="F12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="16" t="n">
         <v>223</v>
       </c>
     </row>
@@ -5380,32 +5254,32 @@
       <c r="F13" s="6" t="n">
         <v>164.9</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <v>164.9</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>Fund Mgmt 59.5% (= Nairne K-1)</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="24" t="n">
+      <c r="G14" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5440,22 +5314,22 @@
           <t>TPA Perf Fees Crystallized (what was OWED)</t>
         </is>
       </c>
-      <c r="B16" s="25" t="n">
+      <c r="B16" s="24" t="n">
         <v>15355.51</v>
       </c>
-      <c r="C16" s="25" t="n">
+      <c r="C16" s="24" t="n">
         <v>12474.75</v>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <v>51906.99</v>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="24" t="n">
         <v>57074.08999999997</v>
       </c>
-      <c r="F16" s="25" t="n">
+      <c r="F16" s="24" t="n">
         <v>16211.69</v>
       </c>
-      <c r="G16" s="25" t="n">
+      <c r="G16" s="24" t="n">
         <v>153023.03</v>
       </c>
     </row>
@@ -5465,22 +5339,22 @@
           <t>DELTA (Owed - Paid; positive = unpaid liability)</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="25" t="n">
         <v>6998.830000000002</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="25" t="n">
         <v>-4056.409999999998</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="25" t="n">
         <v>22315.97</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="25" t="n">
         <v>4083.859999999964</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="25" t="n">
         <v>843.1500000000015</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="25" t="n">
         <v>30185.39999999997</v>
       </c>
     </row>
@@ -5578,170 +5452,157 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>506c SPV Loan</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loan/SPV</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>4275</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>25000</v>
-      </c>
-      <c r="H5" s="17" t="n">
-        <v>29275</v>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>RECLASS: likely balance sheet item (loan/capital), not P&amp;L expense</t>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>RECLASS: likely annual D&amp;O — pro-rate to ~$7,500 for Aug-Dec</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>18000</v>
-      </c>
-      <c r="H6" s="17" t="n">
-        <v>18000</v>
-      </c>
-      <c r="I6" s="21" t="inlineStr">
-        <is>
-          <t>RECLASS: likely annual D&amp;O — pro-rate to ~$7,500 for Aug-Dec</t>
-        </is>
-      </c>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PVD</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PVD (verify)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>6000</v>
+          <t>Marketing/Web</t>
+        </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H7" s="17" t="n">
-        <v>12000</v>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
-        <is>
-          <t>Vendor identification needed for 1099 obligation</t>
+        <v>7500</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>Marketing/web build</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>PVD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Payroll/Contractor</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>7500</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H8" s="17" t="n">
-        <v>11500</v>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
-        <is>
-          <t>Payroll/contractor — likely 1099 (already on consultant 1099 list?)</t>
+          <t>Tech/Ads</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>Vendor identification needed for 1099 obligation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>TPA (second line)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marketing/Web</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>7500</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>7500</v>
-      </c>
-      <c r="I9" s="21" t="inlineStr">
-        <is>
-          <t>Marketing/web build</t>
+          <t>Admin / TPA Fee</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>VERIFY: second TPA line in Dec — separate billing or duplicate?</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ad Spend</t>
+          <t>506c SPV Loan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Marketing/Ads</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
-        <is>
-          <t>Marketing — vendor breakdown needed</t>
+          <t>Loan/SPV</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>4275</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>4275</v>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>RECLASS: likely balance sheet item (loan/capital), not P&amp;L expense</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TPA (second line)</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Admin / TPA Fee</t>
+          <t>Payroll/Contractor</t>
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>4500</v>
-      </c>
-      <c r="I11" s="21" t="inlineStr">
-        <is>
-          <t>VERIFY: second TPA line in Dec — separate billing or duplicate?</t>
+        <v>4000</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>Payroll/contractor — likely 1099 (already on consultant 1099 list?)</t>
         </is>
       </c>
     </row>
@@ -5759,10 +5620,10 @@
       <c r="F12" s="6" t="n">
         <v>2250</v>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="H12" s="16" t="n">
         <v>2250</v>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>Compliance/verification service</t>
         </is>
@@ -5782,10 +5643,10 @@
       <c r="F13" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="16" t="n">
         <v>600</v>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>VERIFY: same as 'TPA (Formidium)' — TPA fee. Confirm GP-paid vs fund-paid.</t>
         </is>
@@ -5805,10 +5666,10 @@
       <c r="G14" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="16" t="n">
         <v>600</v>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>VERIFY: $600/mo also in fund-level admin (TPA books). May double-count.</t>
         </is>
@@ -5828,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>43500</v>
+        <v>7500</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>10350</v>
@@ -5837,7 +5698,7 @@
         <v>27100</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>91225</v>
+        <v>55225</v>
       </c>
       <c r="I15" s="11" t="n"/>
     </row>
@@ -5882,7 +5743,7 @@
       <c r="F20" s="27" t="n"/>
       <c r="G20" s="27" t="n"/>
       <c r="H20" s="28" t="n">
-        <v>51450</v>
+        <v>15450</v>
       </c>
       <c r="I20" s="27" t="n"/>
     </row>
@@ -6002,172 +5863,172 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Nairne — Fund Mgmt 59.5% (Aug: 5.5%)</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n"/>
+      <c r="C5" s="21" t="n"/>
       <c r="D5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="22" t="n"/>
+      <c r="E5" s="21" t="n"/>
       <c r="F5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="22" t="n"/>
+      <c r="G5" s="21" t="n"/>
       <c r="H5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="22" t="n"/>
+      <c r="I5" s="21" t="n"/>
       <c r="J5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="22" t="n"/>
+      <c r="K5" s="21" t="n"/>
       <c r="L5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="24" t="n">
+      <c r="M5" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Nairne — direct 0.5%</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="22" t="n">
         <v>1663.5</v>
       </c>
       <c r="D6" s="29" t="n">
         <v>1663.5</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="22" t="n">
         <v>5845.12</v>
       </c>
       <c r="F6" s="29" t="n">
         <v>7508.62</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="22" t="n">
         <v>6244.65</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>13753.27</v>
       </c>
-      <c r="I6" s="23" t="n">
+      <c r="I6" s="22" t="n">
         <v>15531.01</v>
       </c>
       <c r="J6" s="29" t="n">
         <v>29284.28</v>
       </c>
-      <c r="K6" s="23" t="n">
+      <c r="K6" s="22" t="n">
         <v>4904.6</v>
       </c>
       <c r="L6" s="29" t="n">
         <v>34188.88</v>
       </c>
-      <c r="M6" s="24" t="n">
+      <c r="M6" s="23" t="n">
         <v>34188.88</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Raj Duggal — direct 0.5%</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="22" t="n">
         <v>255.92</v>
       </c>
       <c r="D7" s="29" t="n">
         <v>255.92</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="22" t="n">
         <v>62.32</v>
       </c>
       <c r="F7" s="29" t="n">
         <v>318.24</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="22" t="n">
         <v>262.24</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>580.48</v>
       </c>
-      <c r="I7" s="23" t="n">
+      <c r="I7" s="22" t="n">
         <v>287.26</v>
       </c>
       <c r="J7" s="29" t="n">
         <v>867.74</v>
       </c>
-      <c r="K7" s="23" t="n">
+      <c r="K7" s="22" t="n">
         <v>79.23</v>
       </c>
       <c r="L7" s="29" t="n">
         <v>946.97</v>
       </c>
-      <c r="M7" s="24" t="n">
+      <c r="M7" s="23" t="n">
         <v>946.97</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Phil — direct 0.5%</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>K-1</t>
         </is>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="22" t="n">
         <v>255.92</v>
       </c>
       <c r="D8" s="29" t="n">
         <v>255.92</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="22" t="n">
         <v>62.32</v>
       </c>
       <c r="F8" s="29" t="n">
         <v>318.24</v>
       </c>
-      <c r="G8" s="23" t="n">
+      <c r="G8" s="22" t="n">
         <v>262.24</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>580.48</v>
       </c>
-      <c r="I8" s="23" t="n">
+      <c r="I8" s="22" t="n">
         <v>287.26</v>
       </c>
       <c r="J8" s="29" t="n">
         <v>867.74</v>
       </c>
-      <c r="K8" s="23" t="n">
+      <c r="K8" s="22" t="n">
         <v>79.23</v>
       </c>
       <c r="L8" s="29" t="n">
         <v>946.97</v>
       </c>
-      <c r="M8" s="24" t="n">
+      <c r="M8" s="23" t="n">
         <v>946.97</v>
       </c>
     </row>
@@ -6212,7 +6073,7 @@
       <c r="L9" s="30" t="n">
         <v>38076.87</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="16" t="n">
         <v>38076.87</v>
       </c>
     </row>
@@ -6257,7 +6118,7 @@
       <c r="L10" s="30" t="n">
         <v>37139.89</v>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="16" t="n">
         <v>37139.89</v>
       </c>
     </row>
@@ -6302,7 +6163,7 @@
       <c r="L11" s="30" t="n">
         <v>10388.66</v>
       </c>
-      <c r="M11" s="17" t="n">
+      <c r="M11" s="16" t="n">
         <v>10388.66</v>
       </c>
     </row>
@@ -6341,7 +6202,7 @@
       <c r="L12" s="30" t="n">
         <v>761.49</v>
       </c>
-      <c r="M12" s="17" t="n">
+      <c r="M12" s="16" t="n">
         <v>761.49</v>
       </c>
     </row>
@@ -6374,7 +6235,7 @@
       <c r="L13" s="30" t="n">
         <v>223</v>
       </c>
-      <c r="M13" s="17" t="n">
+      <c r="M13" s="16" t="n">
         <v>223</v>
       </c>
     </row>
@@ -6407,7 +6268,7 @@
       <c r="L14" s="30" t="n">
         <v>164.9</v>
       </c>
-      <c r="M14" s="17" t="n">
+      <c r="M14" s="16" t="n">
         <v>164.9</v>
       </c>
     </row>
@@ -6549,27 +6410,27 @@
         </is>
       </c>
       <c r="B18" s="10" t="n"/>
-      <c r="C18" s="25" t="n">
+      <c r="C18" s="24" t="n">
         <v>15355.51</v>
       </c>
       <c r="D18" s="10" t="n"/>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="24" t="n">
         <v>12474.75</v>
       </c>
       <c r="F18" s="10" t="n"/>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="24" t="n">
         <v>51906.99</v>
       </c>
       <c r="H18" s="10" t="n"/>
-      <c r="I18" s="25" t="n">
+      <c r="I18" s="24" t="n">
         <v>57074.08999999997</v>
       </c>
       <c r="J18" s="10" t="n"/>
-      <c r="K18" s="25" t="n">
+      <c r="K18" s="24" t="n">
         <v>16211.69</v>
       </c>
       <c r="L18" s="10" t="n"/>
-      <c r="M18" s="25" t="n">
+      <c r="M18" s="24" t="n">
         <v>153023.03</v>
       </c>
     </row>
@@ -6580,66 +6441,66 @@
         </is>
       </c>
       <c r="B19" s="10" t="n"/>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="24" t="n">
         <v>10275</v>
       </c>
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
       <c r="F19" s="10" t="n"/>
-      <c r="G19" s="25" t="n">
-        <v>43500</v>
+      <c r="G19" s="24" t="n">
+        <v>7500</v>
       </c>
       <c r="H19" s="10" t="n"/>
-      <c r="I19" s="25" t="n">
+      <c r="I19" s="24" t="n">
         <v>10350</v>
       </c>
       <c r="J19" s="10" t="n"/>
-      <c r="K19" s="25" t="n">
+      <c r="K19" s="24" t="n">
         <v>27100</v>
       </c>
       <c r="L19" s="10" t="n"/>
-      <c r="M19" s="25" t="n">
-        <v>91225</v>
+      <c r="M19" s="24" t="n">
+        <v>55225</v>
       </c>
     </row>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Payouts shown are NET — already after weighted costs (per Nairne 2026-04-30). The Distributions ledger's separate 'Gross vs Net' table tracks cumulative settlement balances (carries forward unpaid amounts) and a layer of Coinbase/wire/Crypto fees (~2.8%) plus per-person 'Expense' allocations (Nairne Expense, Alec Expense, etc.) — those are nested inside the Net amounts you see here.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>TruQuant payments are excluded entirely (per Nairne 2026-04-30). The Aug TruQuant amounts ($6,909.93 Trader &amp; Developer + $88.78 Spydr) and Sep Spydr $82.08 are NOT in any of the rows above.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Aug 2025 used a different waterfall (Fund Mgmt was 5.5% not 59.5%). From Sep onwards: standard 59.5% Mgmt + 39% Consultant + 0.5%×3 principals.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Issac shows -$278.48 in Dec — clawback against prior month overpayment.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Op Expenses row at the bottom is the GP-paid vendor expenses (not allocated to individuals on this tab — see Monthly Op Expenses tab for vendor breakdown).</t>
         </is>

--- a/2025-armada-prime-tech-1099-k1.xlsx
+++ b/2025-armada-prime-tech-1099-k1.xlsx
@@ -3771,14 +3771,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.36%</t>
+          <t>96.80%</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
         <v>34188.88</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>10862.18360655735</v>
+        <v>10689.83695999997</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -3790,14 +3790,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
         <v>946.97</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>90.51819672131126</v>
+        <v>176.6915199999996</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
@@ -3809,14 +3809,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
         <v>946.97</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>90.51819672131126</v>
+        <v>176.6915199999996</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
@@ -3858,21 +3858,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nairne allocated share (98.36%): $10,862.18</t>
+          <t>Nairne allocated share (96.80%): $10,689.84</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Raj allocated share (0.82%): $90.52</t>
+          <t>Raj allocated share (1.60%): $176.69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Phil allocated share (0.82%): $90.52</t>
+          <t>Phil allocated share (1.60%): $176.69</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Ownership % shown (Nairne 98.36%/Raj 0.82%/Phil 0.82%) is derived from the 60/0.5/0.5 split. The actual LLC operating agreement governs — confirm with the accountant before filing.</t>
+          <t>Ownership % shown (Nairne 96.80%/Raj 1.60%/Phil 1.60%) is derived from the 30.25/0.5/0.5 partner split (Nairne's 30.25% = 50%×Fund Mgmt 59.5% + 0.5% direct, per Nairne 2026-05-07). AJ Affleck receives the OTHER 50% of Fund Mgmt 59.5% as a 1099 contractor. The actual LLC operating agreement governs — confirm with the accountant before filing.</t>
         </is>
       </c>
     </row>
